--- a/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BCDTRtSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2672D63-A094-4683-905F-A8926D8DCAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29373D27-92E1-4836-A190-6D1BDD6A0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4293" yWindow="788" windowWidth="15378" windowHeight="13069" tabRatio="742" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4347" yWindow="761" windowWidth="17661" windowHeight="11289" tabRatio="742" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="33" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="122">
   <si>
     <t>Sources:</t>
   </si>
@@ -1920,7 +1920,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2057,8 +2057,33 @@
     <xf numFmtId="183" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="155" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="155" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2071,9 +2096,6 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2105,29 +2127,6 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="155" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="155" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2964,81 +2963,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="H1" s="61" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="H1" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
       <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="68" t="s">
         <v>80</v>
       </c>
       <c r="G2" s="53"/>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="J2" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="L2" s="68" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="41"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="68" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
       <c r="G3" s="53"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
       <c r="M3" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="59"/>
+      <c r="N3" s="68"/>
     </row>
     <row r="4" spans="1:21" ht="13.6" customHeight="1">
       <c r="A4" s="42" t="s">
@@ -3162,14 +3161,14 @@
       <c r="N6" s="44">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="62" t="s">
+      <c r="P6" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+      <c r="U6" s="66"/>
     </row>
     <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="42" t="s">
@@ -3211,18 +3210,18 @@
       <c r="N7" s="44">
         <v>8.18</v>
       </c>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58" t="s">
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="58" t="s">
+      <c r="S7" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="T7" s="58" t="s">
+      <c r="T7" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="58" t="s">
+      <c r="U7" s="67" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3266,12 +3265,12 @@
       <c r="N8" s="44">
         <v>10.1</v>
       </c>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
     </row>
     <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="42" t="s">
@@ -3313,7 +3312,7 @@
       <c r="N9" s="44">
         <v>13.42</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="P9" s="65" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="54">
@@ -3372,7 +3371,7 @@
       <c r="N10" s="44">
         <v>16.61</v>
       </c>
-      <c r="P10" s="57"/>
+      <c r="P10" s="65"/>
       <c r="Q10" s="54">
         <v>2020</v>
       </c>
@@ -3433,7 +3432,7 @@
       <c r="N11" s="44">
         <v>18.579999999999998</v>
       </c>
-      <c r="P11" s="57"/>
+      <c r="P11" s="65"/>
       <c r="Q11" s="54">
         <v>2021</v>
       </c>
@@ -3494,7 +3493,7 @@
       <c r="N12" s="44">
         <v>22.3</v>
       </c>
-      <c r="P12" s="57"/>
+      <c r="P12" s="65"/>
       <c r="Q12" s="54">
         <v>2022</v>
       </c>
@@ -3555,7 +3554,7 @@
       <c r="N13" s="44">
         <v>24.93</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="65" t="s">
         <v>83</v>
       </c>
       <c r="Q13" s="54">
@@ -3614,7 +3613,7 @@
       <c r="N14" s="44">
         <v>29.1</v>
       </c>
-      <c r="P14" s="57"/>
+      <c r="P14" s="65"/>
       <c r="Q14" s="54">
         <v>2020</v>
       </c>
@@ -3675,7 +3674,7 @@
       <c r="N15" s="44">
         <v>33.450000000000003</v>
       </c>
-      <c r="P15" s="57"/>
+      <c r="P15" s="65"/>
       <c r="Q15" s="54">
         <v>2021</v>
       </c>
@@ -3736,7 +3735,7 @@
       <c r="N16" s="44">
         <v>42.34</v>
       </c>
-      <c r="P16" s="57"/>
+      <c r="P16" s="65"/>
       <c r="Q16" s="54">
         <v>2022</v>
       </c>
@@ -3880,14 +3879,14 @@
         <v>51.55</v>
       </c>
       <c r="P19" s="56"/>
-      <c r="Q19" s="57" t="s">
+      <c r="Q19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
     </row>
     <row r="20" spans="1:23" ht="13.6" customHeight="1">
       <c r="A20" s="42" t="s">
@@ -3989,10 +3988,10 @@
         <v>71.8</v>
       </c>
       <c r="P21" s="56"/>
-      <c r="Q21" s="58" t="s">
+      <c r="Q21" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="58"/>
+      <c r="R21" s="67"/>
       <c r="S21" s="55" cm="1">
         <f t="array" ref="S21:V24">TRANSPOSE(R9:U12)</f>
         <v>1</v>
@@ -4052,10 +4051,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P22" s="56"/>
-      <c r="Q22" s="58" t="s">
+      <c r="Q22" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="58"/>
+      <c r="R22" s="67"/>
       <c r="S22" s="55">
         <v>1</v>
       </c>
@@ -4114,10 +4113,10 @@
         <v>94.275260000000003</v>
       </c>
       <c r="P23" s="56"/>
-      <c r="Q23" s="58" t="s">
+      <c r="Q23" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="R23" s="58"/>
+      <c r="R23" s="67"/>
       <c r="S23" s="55">
         <v>1</v>
       </c>
@@ -4176,10 +4175,10 @@
         <v>116.386674</v>
       </c>
       <c r="P24" s="56"/>
-      <c r="Q24" s="58" t="s">
+      <c r="Q24" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="R24" s="58"/>
+      <c r="R24" s="67"/>
       <c r="S24" s="55">
         <v>1</v>
       </c>
@@ -4237,14 +4236,14 @@
       <c r="N25" s="44">
         <v>119.602272</v>
       </c>
-      <c r="Q25" s="57" t="s">
+      <c r="Q25" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="57"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
     </row>
     <row r="26" spans="1:23" ht="13.6" customHeight="1">
       <c r="A26" s="42">
@@ -4339,10 +4338,10 @@
       <c r="N27" s="44">
         <v>178.89815999999999</v>
       </c>
-      <c r="Q27" s="58" t="s">
+      <c r="Q27" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="58"/>
+      <c r="R27" s="67"/>
       <c r="S27" s="55" cm="1">
         <f t="array" ref="S27:V30">TRANSPOSE(R13:U16)</f>
         <v>1</v>
@@ -4397,10 +4396,10 @@
       <c r="N28" s="44">
         <v>173.91</v>
       </c>
-      <c r="Q28" s="58" t="s">
+      <c r="Q28" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="58"/>
+      <c r="R28" s="67"/>
       <c r="S28" s="55">
         <v>1</v>
       </c>
@@ -4454,10 +4453,10 @@
       <c r="N29" s="44">
         <v>163.88936200000001</v>
       </c>
-      <c r="Q29" s="58" t="s">
+      <c r="Q29" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="R29" s="58"/>
+      <c r="R29" s="67"/>
       <c r="S29" s="55">
         <v>1</v>
       </c>
@@ -4511,10 +4510,10 @@
       <c r="N30" s="44">
         <v>170.29181</v>
       </c>
-      <c r="Q30" s="58" t="s">
+      <c r="Q30" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="R30" s="58"/>
+      <c r="R30" s="67"/>
       <c r="S30" s="55">
         <v>1</v>
       </c>
@@ -5114,17 +5113,16 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
@@ -5136,16 +5134,17 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
   </mergeCells>
   <phoneticPr fontId="44" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5165,10 +5164,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="14.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="66"/>
+      <c r="B1" s="74"/>
       <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
@@ -5396,10 +5395,10 @@
       </c>
     </row>
     <row r="2" spans="1:77" ht="14.3">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="72"/>
       <c r="C2" s="11"/>
       <c r="D2" s="12">
         <v>1743.1</v>
@@ -5511,10 +5510,10 @@
       </c>
     </row>
     <row r="3" spans="1:77" ht="14.3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="64"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9">
         <v>1093.22</v>
@@ -5776,10 +5775,10 @@
       </c>
     </row>
     <row r="4" spans="1:77" ht="14.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="64"/>
+      <c r="B4" s="72"/>
       <c r="C4" s="7"/>
       <c r="D4" s="9">
         <v>521.29999999999995</v>
@@ -6041,10 +6040,10 @@
       </c>
     </row>
     <row r="5" spans="1:77" ht="14.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="64"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="7"/>
       <c r="D5" s="9">
         <v>100.63</v>
@@ -9691,174 +9690,174 @@
       </c>
     </row>
     <row r="30" spans="3:77">
-      <c r="D30" s="73" t="s">
+      <c r="D30" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="73">
+      <c r="E30" s="57">
         <f>E29/$E$29</f>
         <v>1</v>
       </c>
-      <c r="F30" s="73">
+      <c r="F30" s="57">
         <f t="shared" ref="F30:K30" si="39">F29/$E$29</f>
         <v>0.53918310508914769</v>
       </c>
-      <c r="G30" s="73">
+      <c r="G30" s="57">
         <f t="shared" si="39"/>
         <v>0.5578413197440476</v>
       </c>
-      <c r="H30" s="73">
+      <c r="H30" s="57">
         <f t="shared" si="39"/>
         <v>0.33436990081416113</v>
       </c>
-      <c r="I30" s="73">
+      <c r="I30" s="57">
         <f t="shared" si="39"/>
         <v>0.88071215603188302</v>
       </c>
-      <c r="J30" s="73">
+      <c r="J30" s="57">
         <f t="shared" si="39"/>
         <v>1.1033207179653663</v>
       </c>
-      <c r="K30" s="73">
+      <c r="K30" s="57">
         <f t="shared" si="39"/>
         <v>1.2495194484549734</v>
       </c>
-      <c r="L30" s="73">
+      <c r="L30" s="57">
         <f t="shared" ref="L30" si="40">L29/$E$29</f>
         <v>1.3240994256313294</v>
       </c>
-      <c r="M30" s="73">
+      <c r="M30" s="57">
         <f t="shared" ref="M30" si="41">M29/$E$29</f>
         <v>1.4031308525250177</v>
       </c>
-      <c r="N30" s="73">
+      <c r="N30" s="57">
         <f t="shared" ref="N30" si="42">N29/$E$29</f>
         <v>1.4868794224941768</v>
       </c>
-      <c r="O30" s="73">
+      <c r="O30" s="57">
         <f t="shared" ref="O30" si="43">O29/$E$29</f>
         <v>1.575626687317246</v>
       </c>
-      <c r="P30" s="73">
+      <c r="P30" s="57">
         <f t="shared" ref="P30" si="44">P29/$E$29</f>
         <v>1.6696710037333518</v>
       </c>
-      <c r="Q30" s="73">
+      <c r="Q30" s="57">
         <f t="shared" ref="Q30" si="45">Q29/$E$29</f>
         <v>1.741146149806418</v>
       </c>
-      <c r="R30" s="73">
+      <c r="R30" s="57">
         <f t="shared" ref="R30" si="46">R29/$E$29</f>
         <v>1.8156809983566449</v>
       </c>
-      <c r="S30" s="73">
+      <c r="S30" s="57">
         <f t="shared" ref="S30" si="47">S29/$E$29</f>
         <v>1.8934065288889803</v>
       </c>
-      <c r="T30" s="73">
+      <c r="T30" s="57">
         <f t="shared" ref="T30" si="48">T29/$E$29</f>
         <v>1.9744593278688025</v>
       </c>
-      <c r="U30" s="73">
+      <c r="U30" s="57">
         <f t="shared" ref="U30" si="49">U29/$E$29</f>
         <v>2.0589818287442441</v>
       </c>
-      <c r="V30" s="73">
+      <c r="V30" s="57">
         <f t="shared" ref="V30" si="50">V29/$E$29</f>
         <v>2.065687093140415</v>
       </c>
-      <c r="W30" s="73">
+      <c r="W30" s="57">
         <f t="shared" ref="W30" si="51">W29/$E$29</f>
         <v>2.0724141938490757</v>
       </c>
-      <c r="X30" s="73">
+      <c r="X30" s="57">
         <f t="shared" ref="X30" si="52">X29/$E$29</f>
         <v>2.0791632019821926</v>
       </c>
-      <c r="Y30" s="73">
+      <c r="Y30" s="57">
         <f t="shared" ref="Y30" si="53">Y29/$E$29</f>
         <v>2.0859341888833169</v>
       </c>
-      <c r="Z30" s="73">
+      <c r="Z30" s="57">
         <f t="shared" ref="Z30" si="54">Z29/$E$29</f>
         <v>2.0927272261283352</v>
       </c>
-      <c r="AA30" s="73">
+      <c r="AA30" s="57">
         <f t="shared" ref="AA30" si="55">AA29/$E$29</f>
         <v>2.1036838040682193</v>
       </c>
-      <c r="AB30" s="73">
+      <c r="AB30" s="57">
         <f t="shared" ref="AB30" si="56">AB29/$E$29</f>
         <v>2.1146977457192713</v>
       </c>
-      <c r="AC30" s="73">
+      <c r="AC30" s="57">
         <f t="shared" ref="AC30" si="57">AC29/$E$29</f>
         <v>2.125769351412067</v>
       </c>
-      <c r="AD30" s="73">
+      <c r="AD30" s="57">
         <f t="shared" ref="AD30" si="58">AD29/$E$29</f>
         <v>2.1368989230495776</v>
       </c>
-      <c r="AE30" s="73">
+      <c r="AE30" s="57">
         <f t="shared" ref="AE30" si="59">AE29/$E$29</f>
         <v>2.1480867641154009</v>
       </c>
-      <c r="AF30" s="73">
+      <c r="AF30" s="57">
         <f t="shared" ref="AF30" si="60">AF29/$E$29</f>
         <v>2.1340474751584533</v>
       </c>
-      <c r="AG30" s="73">
+      <c r="AG30" s="57">
         <f t="shared" ref="AG30" si="61">AG29/$E$29</f>
         <v>2.1200999430326122</v>
       </c>
-      <c r="AH30" s="73">
+      <c r="AH30" s="57">
         <f t="shared" ref="AH30" si="62">AH29/$E$29</f>
         <v>2.1062435680411209</v>
       </c>
-      <c r="AI30" s="73">
+      <c r="AI30" s="57">
         <f t="shared" ref="AI30" si="63">AI29/$E$29</f>
         <v>2.0924777544066706</v>
       </c>
-      <c r="AJ30" s="73">
+      <c r="AJ30" s="57">
         <f t="shared" ref="AJ30" si="64">AJ29/$E$29</f>
         <v>2.0788019102457862</v>
       </c>
-      <c r="AK30" s="73">
+      <c r="AK30" s="57">
         <f t="shared" ref="AK30" si="65">AK29/$E$29</f>
         <v>2.0319917609957465</v>
       </c>
-      <c r="AL30" s="73">
+      <c r="AL30" s="57">
         <f t="shared" ref="AL30" si="66">AL29/$E$29</f>
         <v>1.9862356756572381</v>
       </c>
-      <c r="AM30" s="73">
+      <c r="AM30" s="57">
         <f t="shared" ref="AM30" si="67">AM29/$E$29</f>
         <v>1.9415099189773843</v>
       </c>
-      <c r="AN30" s="73">
+      <c r="AN30" s="57">
         <f t="shared" ref="AN30" si="68">AN29/$E$29</f>
         <v>1.8977912901701703</v>
       </c>
-      <c r="AO30" s="73">
+      <c r="AO30" s="57">
         <f t="shared" ref="AO30" si="69">AO29/$E$29</f>
         <v>1.8550571108813958</v>
       </c>
-      <c r="AP30" s="73">
+      <c r="AP30" s="57">
         <f t="shared" ref="AP30" si="70">AP29/$E$29</f>
         <v>1.7962182767856762</v>
       </c>
-      <c r="AQ30" s="73">
+      <c r="AQ30" s="57">
         <f t="shared" ref="AQ30" si="71">AQ29/$E$29</f>
         <v>1.7392456970372951</v>
       </c>
-      <c r="AR30" s="73">
+      <c r="AR30" s="57">
         <f t="shared" ref="AR30" si="72">AR29/$E$29</f>
         <v>1.6840801776474104</v>
       </c>
-      <c r="AS30" s="73">
+      <c r="AS30" s="57">
         <f t="shared" ref="AS30" si="73">AS29/$E$29</f>
         <v>1.6306644021463503</v>
       </c>
-      <c r="AT30" s="73">
+      <c r="AT30" s="57">
         <f t="shared" ref="AT30" si="74">AT29/$E$29</f>
         <v>1.5789428720323273</v>
       </c>
@@ -9998,174 +9997,174 @@
       </c>
     </row>
     <row r="32" spans="3:77">
-      <c r="D32" s="73" t="s">
+      <c r="D32" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="73">
+      <c r="E32" s="57">
         <f>E31/$E31</f>
         <v>1</v>
       </c>
-      <c r="F32" s="73">
+      <c r="F32" s="57">
         <f t="shared" ref="F32:J32" si="75">F31/$E$31</f>
         <v>0.56207417078046595</v>
       </c>
-      <c r="G32" s="73">
+      <c r="G32" s="57">
         <f t="shared" si="75"/>
         <v>0.65057865176179397</v>
       </c>
-      <c r="H32" s="73">
+      <c r="H32" s="57">
         <f t="shared" si="75"/>
         <v>0.44724817428909469</v>
       </c>
-      <c r="I32" s="73">
+      <c r="I32" s="57">
         <f t="shared" si="75"/>
         <v>1.0015503243441719</v>
       </c>
-      <c r="J32" s="73">
+      <c r="J32" s="57">
         <f t="shared" si="75"/>
         <v>1.0742863748249085</v>
       </c>
-      <c r="K32" s="73">
+      <c r="K32" s="57">
         <f>K31/$E$31</f>
         <v>1.0609864571130831</v>
       </c>
-      <c r="L32" s="73">
+      <c r="L32" s="57">
         <f t="shared" ref="L32" si="76">L31/$E$31</f>
         <v>1.092014418521257</v>
       </c>
-      <c r="M32" s="73">
+      <c r="M32" s="57">
         <f t="shared" ref="M32" si="77">M31/$E$31</f>
         <v>1.1239497754788206</v>
       </c>
-      <c r="N32" s="73">
+      <c r="N32" s="57">
         <f t="shared" ref="N32" si="78">N31/$E$31</f>
         <v>1.156819064266138</v>
       </c>
-      <c r="O32" s="73">
+      <c r="O32" s="57">
         <f t="shared" ref="O32" si="79">O31/$E$31</f>
         <v>1.1906495972023974</v>
       </c>
-      <c r="P32" s="73">
+      <c r="P32" s="57">
         <f t="shared" ref="P32" si="80">P31/$E$31</f>
         <v>1.2254694853404384</v>
       </c>
-      <c r="Q32" s="73">
+      <c r="Q32" s="57">
         <f t="shared" ref="Q32" si="81">Q31/$E$31</f>
         <v>1.2613076618252728</v>
       </c>
-      <c r="R32" s="73">
+      <c r="R32" s="57">
         <f t="shared" ref="R32" si="82">R31/$E$31</f>
         <v>1.2981939059357173</v>
       </c>
-      <c r="S32" s="73">
+      <c r="S32" s="57">
         <f t="shared" ref="S32" si="83">S31/$E$31</f>
         <v>1.3361588678291063</v>
       </c>
-      <c r="T32" s="73">
+      <c r="T32" s="57">
         <f t="shared" ref="T32" si="84">T31/$E$31</f>
         <v>1.3752340940096532</v>
       </c>
-      <c r="U32" s="73">
+      <c r="U32" s="57">
         <f t="shared" ref="U32" si="85">U31/$E$31</f>
         <v>1.415452053541618</v>
       </c>
-      <c r="V32" s="73">
+      <c r="V32" s="57">
         <f t="shared" ref="V32" si="86">V31/$E$31</f>
         <v>1.4437610946124506</v>
       </c>
-      <c r="W32" s="73">
+      <c r="W32" s="57">
         <f t="shared" ref="W32" si="87">W31/$E$31</f>
         <v>1.4726363165046996</v>
       </c>
-      <c r="X32" s="73">
+      <c r="X32" s="57">
         <f t="shared" ref="X32" si="88">X31/$E$31</f>
         <v>1.5020890428347937</v>
       </c>
-      <c r="Y32" s="73">
+      <c r="Y32" s="57">
         <f t="shared" ref="Y32" si="89">Y31/$E$31</f>
         <v>1.5321308236914897</v>
       </c>
-      <c r="Z32" s="73">
+      <c r="Z32" s="57">
         <f t="shared" ref="Z32" si="90">Z31/$E$31</f>
         <v>1.5627734401653193</v>
       </c>
-      <c r="AA32" s="73">
+      <c r="AA32" s="57">
         <f t="shared" ref="AA32" si="91">AA31/$E$31</f>
         <v>1.5940289089686257</v>
       </c>
-      <c r="AB32" s="73">
+      <c r="AB32" s="57">
         <f t="shared" ref="AB32" si="92">AB31/$E$31</f>
         <v>1.6259094871479984</v>
       </c>
-      <c r="AC32" s="73">
+      <c r="AC32" s="57">
         <f t="shared" ref="AC32" si="93">AC31/$E$31</f>
         <v>1.6584276768909583</v>
       </c>
-      <c r="AD32" s="73">
+      <c r="AD32" s="57">
         <f t="shared" ref="AD32" si="94">AD31/$E$31</f>
         <v>1.6915962304287775</v>
       </c>
-      <c r="AE32" s="73">
+      <c r="AE32" s="57">
         <f t="shared" ref="AE32" si="95">AE31/$E$31</f>
         <v>1.7254281550373531</v>
       </c>
-      <c r="AF32" s="73">
+      <c r="AF32" s="57">
         <f t="shared" ref="AF32" si="96">AF31/$E$31</f>
         <v>1.7426824365877267</v>
       </c>
-      <c r="AG32" s="73">
+      <c r="AG32" s="57">
         <f t="shared" ref="AG32" si="97">AG31/$E$31</f>
         <v>1.760109260953604</v>
       </c>
-      <c r="AH32" s="73">
+      <c r="AH32" s="57">
         <f t="shared" ref="AH32" si="98">AH31/$E$31</f>
         <v>1.77771035356314</v>
       </c>
-      <c r="AI32" s="73">
+      <c r="AI32" s="57">
         <f t="shared" ref="AI32" si="99">AI31/$E$31</f>
         <v>1.7954874570987716</v>
       </c>
-      <c r="AJ32" s="73">
+      <c r="AJ32" s="57">
         <f t="shared" ref="AJ32" si="100">AJ31/$E$31</f>
         <v>1.8134423316697592</v>
       </c>
-      <c r="AK32" s="73">
+      <c r="AK32" s="57">
         <f t="shared" ref="AK32" si="101">AK31/$E$31</f>
         <v>1.8315767549864568</v>
       </c>
-      <c r="AL32" s="73">
+      <c r="AL32" s="57">
         <f t="shared" ref="AL32" si="102">AL31/$E$31</f>
         <v>1.8498925225363214</v>
       </c>
-      <c r="AM32" s="73">
+      <c r="AM32" s="57">
         <f t="shared" ref="AM32" si="103">AM31/$E$31</f>
         <v>1.8683914477616848</v>
       </c>
-      <c r="AN32" s="73">
+      <c r="AN32" s="57">
         <f t="shared" ref="AN32" si="104">AN31/$E$31</f>
         <v>1.8870753622393015</v>
       </c>
-      <c r="AO32" s="73">
+      <c r="AO32" s="57">
         <f t="shared" ref="AO32" si="105">AO31/$E$31</f>
         <v>1.8870753622393015</v>
       </c>
-      <c r="AP32" s="73">
+      <c r="AP32" s="57">
         <f t="shared" ref="AP32" si="106">AP31/$E$31</f>
         <v>1.8965107390504978</v>
       </c>
-      <c r="AQ32" s="73">
+      <c r="AQ32" s="57">
         <f t="shared" ref="AQ32" si="107">AQ31/$E$31</f>
         <v>1.9059932927457501</v>
       </c>
-      <c r="AR32" s="73">
+      <c r="AR32" s="57">
         <f t="shared" ref="AR32" si="108">AR31/$E$31</f>
         <v>1.9155232592094786</v>
       </c>
-      <c r="AS32" s="73">
+      <c r="AS32" s="57">
         <f t="shared" ref="AS32" si="109">AS31/$E$31</f>
         <v>1.9251008755055259</v>
       </c>
-      <c r="AT32" s="73">
+      <c r="AT32" s="57">
         <f t="shared" ref="AT32" si="110">AT31/$E$31</f>
         <v>1.9347263798830534</v>
       </c>
@@ -10305,872 +10304,872 @@
       </c>
     </row>
     <row r="34" spans="3:46">
-      <c r="D34" s="73" t="s">
+      <c r="D34" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="73">
+      <c r="E34" s="57">
         <f>E33/$E33</f>
         <v>1</v>
       </c>
-      <c r="F34" s="73">
+      <c r="F34" s="57">
         <f t="shared" ref="F34:J34" si="111">F33/$E33</f>
         <v>0.41147132169576056</v>
       </c>
-      <c r="G34" s="73">
+      <c r="G34" s="57">
         <f t="shared" si="111"/>
         <v>0.41271820448877805</v>
       </c>
-      <c r="H34" s="73">
+      <c r="H34" s="57">
         <f t="shared" si="111"/>
         <v>0.28179551122194513</v>
       </c>
-      <c r="I34" s="73">
+      <c r="I34" s="57">
         <f t="shared" si="111"/>
         <v>0.67082294264339148</v>
       </c>
-      <c r="J34" s="73">
+      <c r="J34" s="57">
         <f t="shared" si="111"/>
         <v>0.68204488778054861</v>
       </c>
-      <c r="K34" s="73">
+      <c r="K34" s="57">
         <f t="shared" ref="K34" si="112">K33/$E33</f>
         <v>0.69792418952618451</v>
       </c>
-      <c r="L34" s="73">
+      <c r="L34" s="57">
         <f t="shared" ref="L34" si="113">L33/$E33</f>
         <v>0.71188267331670829</v>
       </c>
-      <c r="M34" s="73">
+      <c r="M34" s="57">
         <f t="shared" ref="M34" si="114">M33/$E33</f>
         <v>0.72612032678304239</v>
       </c>
-      <c r="N34" s="73">
+      <c r="N34" s="57">
         <f t="shared" ref="N34" si="115">N33/$E33</f>
         <v>0.74064273331870334</v>
       </c>
-      <c r="O34" s="73">
+      <c r="O34" s="57">
         <f t="shared" ref="O34" si="116">O33/$E33</f>
         <v>0.75545558798507739</v>
       </c>
-      <c r="P34" s="73">
+      <c r="P34" s="57">
         <f t="shared" ref="P34" si="117">P33/$E33</f>
         <v>0.77056469974477904</v>
       </c>
-      <c r="Q34" s="73">
+      <c r="Q34" s="57">
         <f t="shared" ref="Q34" si="118">Q33/$E33</f>
         <v>0.78597599373967464</v>
       </c>
-      <c r="R34" s="73">
+      <c r="R34" s="57">
         <f t="shared" ref="R34" si="119">R33/$E33</f>
         <v>0.80169551361446811</v>
       </c>
-      <c r="S34" s="73">
+      <c r="S34" s="57">
         <f t="shared" ref="S34" si="120">S33/$E33</f>
         <v>0.81772942388675751</v>
       </c>
-      <c r="T34" s="73">
+      <c r="T34" s="57">
         <f t="shared" ref="T34" si="121">T33/$E33</f>
         <v>0.83408401236449281</v>
       </c>
-      <c r="U34" s="73">
+      <c r="U34" s="57">
         <f t="shared" ref="U34" si="122">U33/$E33</f>
         <v>0.85076569261178281</v>
       </c>
-      <c r="V34" s="73">
+      <c r="V34" s="57">
         <f t="shared" ref="V34" si="123">V33/$E33</f>
         <v>0.85501952107484169</v>
       </c>
-      <c r="W34" s="73">
+      <c r="W34" s="57">
         <f t="shared" ref="W34" si="124">W33/$E33</f>
         <v>0.85929461868021584</v>
       </c>
-      <c r="X34" s="73">
+      <c r="X34" s="57">
         <f t="shared" ref="X34" si="125">X33/$E33</f>
         <v>0.86359109177361681</v>
       </c>
-      <c r="Y34" s="73">
+      <c r="Y34" s="57">
         <f t="shared" ref="Y34" si="126">Y33/$E33</f>
         <v>0.86790904723248463</v>
       </c>
-      <c r="Z34" s="73">
+      <c r="Z34" s="57">
         <f t="shared" ref="Z34" si="127">Z33/$E33</f>
         <v>0.87224859246864705</v>
       </c>
-      <c r="AA34" s="73">
+      <c r="AA34" s="57">
         <f t="shared" ref="AA34" si="128">AA33/$E33</f>
         <v>0.87660983543099025</v>
       </c>
-      <c r="AB34" s="73">
+      <c r="AB34" s="57">
         <f t="shared" ref="AB34" si="129">AB33/$E33</f>
         <v>0.88099288460814518</v>
       </c>
-      <c r="AC34" s="73">
+      <c r="AC34" s="57">
         <f t="shared" ref="AC34" si="130">AC33/$E33</f>
         <v>0.88539784903118579</v>
       </c>
-      <c r="AD34" s="73">
+      <c r="AD34" s="57">
         <f t="shared" ref="AD34" si="131">AD33/$E33</f>
         <v>0.88982483827634162</v>
       </c>
-      <c r="AE34" s="73">
+      <c r="AE34" s="57">
         <f t="shared" ref="AE34" si="132">AE33/$E33</f>
         <v>0.89427396246772328</v>
       </c>
-      <c r="AF34" s="73">
+      <c r="AF34" s="57">
         <f t="shared" ref="AF34" si="133">AF33/$E33</f>
         <v>0.89606251039265872</v>
       </c>
-      <c r="AG34" s="73">
+      <c r="AG34" s="57">
         <f t="shared" ref="AG34" si="134">AG33/$E33</f>
         <v>0.89785463541344412</v>
       </c>
-      <c r="AH34" s="73">
+      <c r="AH34" s="57">
         <f t="shared" ref="AH34" si="135">AH33/$E33</f>
         <v>0.89965034468427085</v>
       </c>
-      <c r="AI34" s="73">
+      <c r="AI34" s="57">
         <f t="shared" ref="AI34" si="136">AI33/$E33</f>
         <v>0.90144964537363936</v>
       </c>
-      <c r="AJ34" s="73">
+      <c r="AJ34" s="57">
         <f t="shared" ref="AJ34" si="137">AJ33/$E33</f>
         <v>0.90325254466438676</v>
       </c>
-      <c r="AK34" s="73">
+      <c r="AK34" s="57">
         <f t="shared" ref="AK34" si="138">AK33/$E33</f>
         <v>0.90505904975371543</v>
       </c>
-      <c r="AL34" s="73">
+      <c r="AL34" s="57">
         <f t="shared" ref="AL34" si="139">AL33/$E33</f>
         <v>0.90686916785322291</v>
       </c>
-      <c r="AM34" s="73">
+      <c r="AM34" s="57">
         <f t="shared" ref="AM34" si="140">AM33/$E33</f>
         <v>0.90868290618892933</v>
       </c>
-      <c r="AN34" s="73">
+      <c r="AN34" s="57">
         <f t="shared" ref="AN34" si="141">AN33/$E33</f>
         <v>0.91050027200130723</v>
       </c>
-      <c r="AO34" s="73">
+      <c r="AO34" s="57">
         <f t="shared" ref="AO34" si="142">AO33/$E33</f>
         <v>0.91050027200130723</v>
       </c>
-      <c r="AP34" s="73">
+      <c r="AP34" s="57">
         <f t="shared" ref="AP34" si="143">AP33/$E33</f>
         <v>0.91232127254530981</v>
       </c>
-      <c r="AQ34" s="73">
+      <c r="AQ34" s="57">
         <f t="shared" ref="AQ34" si="144">AQ33/$E33</f>
         <v>0.91414591509040033</v>
       </c>
-      <c r="AR34" s="73">
+      <c r="AR34" s="57">
         <f t="shared" ref="AR34" si="145">AR33/$E33</f>
         <v>0.91597420692058129</v>
       </c>
-      <c r="AS34" s="73">
+      <c r="AS34" s="57">
         <f t="shared" ref="AS34" si="146">AS33/$E33</f>
         <v>0.91780615533442234</v>
       </c>
-      <c r="AT34" s="73">
+      <c r="AT34" s="57">
         <f t="shared" ref="AT34" si="147">AT33/$E33</f>
         <v>0.9196417676450912</v>
       </c>
     </row>
-    <row r="35" spans="3:46" s="81" customFormat="1">
-      <c r="C35" s="81" t="s">
+    <row r="35" spans="3:46">
+      <c r="C35" t="s">
         <v>66</v>
       </c>
       <c r="D35" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="81">
+      <c r="E35">
         <f>E41+E42</f>
         <v>40404.152501724369</v>
       </c>
-      <c r="F35" s="81">
+      <c r="F35">
         <f t="shared" ref="F35:O35" si="148">F41+F42</f>
         <v>37647.358320109633</v>
       </c>
-      <c r="G35" s="81">
+      <c r="G35">
         <f t="shared" si="148"/>
         <v>39816.103110580858</v>
       </c>
-      <c r="H35" s="81">
+      <c r="H35">
         <f t="shared" si="148"/>
         <v>38580.837164949124</v>
       </c>
-      <c r="I35" s="81">
+      <c r="I35">
         <f t="shared" si="148"/>
         <v>37514.213096250001</v>
       </c>
-      <c r="J35" s="81">
+      <c r="J35">
         <f t="shared" si="148"/>
         <v>37015.327399328584</v>
       </c>
-      <c r="K35" s="81">
+      <c r="K35">
         <f t="shared" si="148"/>
         <v>38945.826080989827</v>
       </c>
-      <c r="L35" s="81">
+      <c r="L35">
         <f t="shared" si="148"/>
         <v>40714.742013766692</v>
       </c>
-      <c r="M35" s="81">
+      <c r="M35">
         <f t="shared" si="148"/>
         <v>42064.826527197823</v>
       </c>
-      <c r="N35" s="81">
+      <c r="N35">
         <f t="shared" si="148"/>
         <v>43127.57517350679</v>
       </c>
-      <c r="O35" s="81">
+      <c r="O35">
         <f t="shared" si="148"/>
         <v>43982.299598038211</v>
       </c>
-      <c r="P35" s="81">
+      <c r="P35">
         <f t="shared" ref="P35:AP35" si="149">P41+P42</f>
         <v>44726.149946288126</v>
       </c>
-      <c r="Q35" s="81">
+      <c r="Q35">
         <f t="shared" si="149"/>
         <v>45343.781535297574</v>
       </c>
-      <c r="R35" s="81">
+      <c r="R35">
         <f t="shared" si="149"/>
         <v>45902.018979910885</v>
       </c>
-      <c r="S35" s="81">
+      <c r="S35">
         <f t="shared" si="149"/>
         <v>46372.122266823113</v>
       </c>
-      <c r="T35" s="81">
+      <c r="T35">
         <f t="shared" si="149"/>
         <v>46754.478376104664</v>
       </c>
-      <c r="U35" s="81">
+      <c r="U35">
         <f t="shared" si="149"/>
         <v>47034.894997192525</v>
       </c>
-      <c r="V35" s="81">
+      <c r="V35">
         <f t="shared" si="149"/>
         <v>47255.584808148706</v>
       </c>
-      <c r="W35" s="81">
+      <c r="W35">
         <f t="shared" si="149"/>
         <v>47390.819739572122</v>
       </c>
-      <c r="X35" s="81">
+      <c r="X35">
         <f t="shared" si="149"/>
         <v>47452.39710058221</v>
       </c>
-      <c r="Y35" s="81">
+      <c r="Y35">
         <f t="shared" si="149"/>
         <v>47446.810391801555</v>
       </c>
-      <c r="Z35" s="81">
+      <c r="Z35">
         <f t="shared" si="149"/>
         <v>47379.722838498863</v>
       </c>
-      <c r="AA35" s="81">
+      <c r="AA35">
         <f t="shared" si="149"/>
         <v>47260.872531611429</v>
       </c>
-      <c r="AB35" s="81">
+      <c r="AB35">
         <f t="shared" si="149"/>
         <v>47089.335408015497</v>
       </c>
-      <c r="AC35" s="81">
+      <c r="AC35">
         <f t="shared" si="149"/>
         <v>46869.683008907472</v>
       </c>
-      <c r="AD35" s="81">
+      <c r="AD35">
         <f t="shared" si="149"/>
         <v>46606.582742589482</v>
       </c>
-      <c r="AE35" s="81">
+      <c r="AE35">
         <f t="shared" si="149"/>
         <v>46303.661195475586</v>
       </c>
-      <c r="AF35" s="81">
+      <c r="AF35">
         <f t="shared" si="149"/>
         <v>45966.789291628986</v>
       </c>
-      <c r="AG35" s="81">
+      <c r="AG35">
         <f t="shared" si="149"/>
         <v>45596.470469612585</v>
       </c>
-      <c r="AH35" s="81">
+      <c r="AH35">
         <f t="shared" si="149"/>
         <v>45196.028947519459</v>
       </c>
-      <c r="AI35" s="81">
+      <c r="AI35">
         <f t="shared" si="149"/>
         <v>44769.525627499424</v>
       </c>
-      <c r="AJ35" s="81">
+      <c r="AJ35">
         <f t="shared" si="149"/>
         <v>44320.156820994103</v>
       </c>
-      <c r="AK35" s="81">
+      <c r="AK35">
         <f t="shared" si="149"/>
         <v>43858.102802805799</v>
       </c>
-      <c r="AL35" s="81">
+      <c r="AL35">
         <f t="shared" si="149"/>
         <v>43370.869247706942</v>
       </c>
-      <c r="AM35" s="81">
+      <c r="AM35">
         <f t="shared" si="149"/>
         <v>42858.864539594484</v>
       </c>
-      <c r="AN35" s="81">
+      <c r="AN35">
         <f t="shared" si="149"/>
         <v>42322.193625002896</v>
       </c>
-      <c r="AO35" s="81">
+      <c r="AO35">
         <f t="shared" si="149"/>
         <v>41760.707547394813</v>
       </c>
-      <c r="AP35" s="81">
+      <c r="AP35">
         <f t="shared" si="149"/>
         <v>41173.903256058285</v>
       </c>
-      <c r="AQ35" s="81">
+      <c r="AQ35">
         <f>AQ41+AQ42</f>
         <v>40561.26036433519</v>
       </c>
-      <c r="AR35" s="81">
+      <c r="AR35">
         <f t="shared" ref="AR35:AT35" si="150">AR41+AR42</f>
         <v>39922.126435311853</v>
       </c>
-      <c r="AS35" s="81">
+      <c r="AS35">
         <f t="shared" si="150"/>
         <v>39255.711187499692</v>
       </c>
-      <c r="AT35" s="81">
+      <c r="AT35">
         <f t="shared" si="150"/>
         <v>38561.535692607569</v>
       </c>
     </row>
     <row r="36" spans="3:46">
-      <c r="D36" s="73" t="s">
+      <c r="D36" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="73">
+      <c r="E36" s="57">
         <f>E35/$E35</f>
         <v>1</v>
       </c>
-      <c r="F36" s="73">
+      <c r="F36" s="57">
         <f t="shared" ref="F36:O36" si="151">F35/$E35</f>
         <v>0.93176953330484824</v>
       </c>
-      <c r="G36" s="73">
+      <c r="G36" s="57">
         <f t="shared" si="151"/>
         <v>0.98544581794857811</v>
       </c>
-      <c r="H36" s="73">
+      <c r="H36" s="57">
         <f t="shared" si="151"/>
         <v>0.95487307061576332</v>
       </c>
-      <c r="I36" s="73">
+      <c r="I36" s="57">
         <f t="shared" si="151"/>
         <v>0.92847419815695842</v>
       </c>
-      <c r="J36" s="73">
+      <c r="J36" s="57">
         <f t="shared" si="151"/>
         <v>0.91612681141496144</v>
       </c>
-      <c r="K36" s="73">
+      <c r="K36" s="57">
         <f t="shared" si="151"/>
         <v>0.9639065212252057</v>
       </c>
-      <c r="L36" s="73">
+      <c r="L36" s="57">
         <f t="shared" si="151"/>
         <v>1.007687069095907</v>
       </c>
-      <c r="M36" s="73">
+      <c r="M36" s="57">
         <f t="shared" si="151"/>
         <v>1.0411015680975508</v>
       </c>
-      <c r="N36" s="73">
+      <c r="N36" s="57">
         <f t="shared" si="151"/>
         <v>1.0674045241183117</v>
       </c>
-      <c r="O36" s="73">
+      <c r="O36" s="57">
         <f t="shared" si="151"/>
         <v>1.0885588949344038</v>
       </c>
-      <c r="P36" s="73">
+      <c r="P36" s="57">
         <f t="shared" ref="P36" si="152">P35/$E35</f>
         <v>1.1069691399758801</v>
       </c>
-      <c r="Q36" s="73">
+      <c r="Q36" s="57">
         <f t="shared" ref="Q36" si="153">Q35/$E35</f>
         <v>1.1222554793931736</v>
       </c>
-      <c r="R36" s="73">
+      <c r="R36" s="57">
         <f t="shared" ref="R36" si="154">R35/$E35</f>
         <v>1.1360718178150595</v>
       </c>
-      <c r="S36" s="73">
+      <c r="S36" s="57">
         <f t="shared" ref="S36" si="155">S35/$E35</f>
         <v>1.1477068418857206</v>
       </c>
-      <c r="T36" s="73">
+      <c r="T36" s="57">
         <f t="shared" ref="T36" si="156">T35/$E35</f>
         <v>1.1571701293353269</v>
       </c>
-      <c r="U36" s="73">
+      <c r="U36" s="57">
         <f t="shared" ref="U36" si="157">U35/$E35</f>
         <v>1.1641104214519824</v>
       </c>
-      <c r="V36" s="73">
+      <c r="V36" s="57">
         <f t="shared" ref="V36" si="158">V35/$E35</f>
         <v>1.1695724791191184</v>
       </c>
-      <c r="W36" s="73">
+      <c r="W36" s="57">
         <f t="shared" ref="W36" si="159">W35/$E35</f>
         <v>1.1729195343857188</v>
       </c>
-      <c r="X36" s="73">
+      <c r="X36" s="57">
         <f t="shared" ref="X36:Y36" si="160">X35/$E35</f>
         <v>1.1744435698424076</v>
       </c>
-      <c r="Y36" s="73">
+      <c r="Y36" s="57">
         <f t="shared" si="160"/>
         <v>1.1743052991837069</v>
       </c>
-      <c r="Z36" s="73">
+      <c r="Z36" s="57">
         <f t="shared" ref="Z36" si="161">Z35/$E35</f>
         <v>1.1726448868461425</v>
       </c>
-      <c r="AA36" s="73">
+      <c r="AA36" s="57">
         <f t="shared" ref="AA36" si="162">AA35/$E35</f>
         <v>1.1697033499117306</v>
       </c>
-      <c r="AB36" s="73">
+      <c r="AB36" s="57">
         <f t="shared" ref="AB36" si="163">AB35/$E35</f>
         <v>1.1654578178816104</v>
       </c>
-      <c r="AC36" s="73">
+      <c r="AC36" s="57">
         <f t="shared" ref="AC36" si="164">AC35/$E35</f>
         <v>1.1600214360864807</v>
       </c>
-      <c r="AD36" s="73">
+      <c r="AD36" s="57">
         <f t="shared" ref="AD36" si="165">AD35/$E35</f>
         <v>1.1535097225613236</v>
       </c>
-      <c r="AE36" s="73">
+      <c r="AE36" s="57">
         <f t="shared" ref="AE36" si="166">AE35/$E35</f>
         <v>1.1460124350708616</v>
       </c>
-      <c r="AF36" s="73">
+      <c r="AF36" s="57">
         <f t="shared" ref="AF36" si="167">AF35/$E35</f>
         <v>1.1376748785825224</v>
       </c>
-      <c r="AG36" s="73">
+      <c r="AG36" s="57">
         <f t="shared" ref="AG36" si="168">AG35/$E35</f>
         <v>1.1285095131661682</v>
       </c>
-      <c r="AH36" s="73">
+      <c r="AH36" s="57">
         <f t="shared" ref="AH36:AI36" si="169">AH35/$E35</f>
         <v>1.1185986129913399</v>
       </c>
-      <c r="AI36" s="73">
+      <c r="AI36" s="57">
         <f t="shared" si="169"/>
         <v>1.108042685107397</v>
       </c>
-      <c r="AJ36" s="73">
+      <c r="AJ36" s="57">
         <f t="shared" ref="AJ36" si="170">AJ35/$E35</f>
         <v>1.0969208380030395</v>
       </c>
-      <c r="AK36" s="73">
+      <c r="AK36" s="57">
         <f t="shared" ref="AK36" si="171">AK35/$E35</f>
         <v>1.0854850327805792</v>
       </c>
-      <c r="AL36" s="73">
+      <c r="AL36" s="57">
         <f t="shared" ref="AL36" si="172">AL35/$E35</f>
         <v>1.073426035748577</v>
       </c>
-      <c r="AM36" s="73">
+      <c r="AM36" s="57">
         <f t="shared" ref="AM36" si="173">AM35/$E35</f>
         <v>1.0607539543804403</v>
       </c>
-      <c r="AN36" s="73">
+      <c r="AN36" s="57">
         <f t="shared" ref="AN36" si="174">AN35/$E35</f>
         <v>1.0474713860956908</v>
       </c>
-      <c r="AO36" s="73">
+      <c r="AO36" s="57">
         <f t="shared" ref="AO36" si="175">AO35/$E35</f>
         <v>1.0335746442302569</v>
       </c>
-      <c r="AP36" s="73">
+      <c r="AP36" s="57">
         <f t="shared" ref="AP36" si="176">AP35/$E35</f>
         <v>1.019051278313561</v>
       </c>
-      <c r="AQ36" s="73">
+      <c r="AQ36" s="57">
         <f>AQ35/$E35</f>
         <v>1.0038884088115476</v>
       </c>
-      <c r="AR36" s="73">
+      <c r="AR36" s="57">
         <f t="shared" ref="AR36" si="177">AR35/$E35</f>
         <v>0.98806988795540396</v>
       </c>
-      <c r="AS36" s="73">
+      <c r="AS36" s="57">
         <f t="shared" ref="AS36" si="178">AS35/$E35</f>
         <v>0.97157615633255356</v>
       </c>
-      <c r="AT36" s="73">
+      <c r="AT36" s="57">
         <f t="shared" ref="AT36" si="179">AT35/$E35</f>
         <v>0.95439536050067719</v>
       </c>
     </row>
-    <row r="37" spans="3:46" s="81" customFormat="1">
-      <c r="C37" s="81" t="s">
+    <row r="37" spans="3:46">
+      <c r="C37" t="s">
         <v>52</v>
       </c>
       <c r="D37" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="81">
+      <c r="E37">
         <f>E43+E44</f>
         <v>20683.626500000006</v>
       </c>
-      <c r="F37" s="81">
+      <c r="F37">
         <f t="shared" ref="F37:O37" si="180">F43+F44</f>
         <v>15024.313599999992</v>
       </c>
-      <c r="G37" s="81">
+      <c r="G37">
         <f t="shared" si="180"/>
         <v>14677.074724999997</v>
       </c>
-      <c r="H37" s="81">
+      <c r="H37">
         <f t="shared" si="180"/>
         <v>13325.719208313925</v>
       </c>
-      <c r="I37" s="81">
+      <c r="I37">
         <f t="shared" si="180"/>
         <v>15802.422465132951</v>
       </c>
-      <c r="J37" s="81">
+      <c r="J37">
         <f t="shared" si="180"/>
         <v>15742.833551444439</v>
       </c>
-      <c r="K37" s="81">
+      <c r="K37">
         <f t="shared" si="180"/>
         <v>15674.562723964056</v>
       </c>
-      <c r="L37" s="81">
+      <c r="L37">
         <f t="shared" si="180"/>
         <v>15608.444391811085</v>
       </c>
-      <c r="M37" s="81">
+      <c r="M37">
         <f t="shared" si="180"/>
         <v>15554.390665093806</v>
       </c>
-      <c r="N37" s="81">
+      <c r="N37">
         <f t="shared" si="180"/>
         <v>15508.219462685473</v>
       </c>
-      <c r="O37" s="81">
+      <c r="O37">
         <f t="shared" si="180"/>
         <v>15467.436256218141</v>
       </c>
-      <c r="P37" s="81">
+      <c r="P37">
         <f t="shared" ref="P37:AP37" si="181">P43+P44</f>
         <v>15428.064352163685</v>
       </c>
-      <c r="Q37" s="81">
+      <c r="Q37">
         <f t="shared" si="181"/>
         <v>15391.125952468414</v>
       </c>
-      <c r="R37" s="81">
+      <c r="R37">
         <f t="shared" si="181"/>
         <v>15353.11281919395</v>
       </c>
-      <c r="S37" s="81">
+      <c r="S37">
         <f t="shared" si="181"/>
         <v>15315.559839093825</v>
       </c>
-      <c r="T37" s="81">
+      <c r="T37">
         <f t="shared" si="181"/>
         <v>15278.611440056833</v>
       </c>
-      <c r="U37" s="81">
+      <c r="U37">
         <f t="shared" si="181"/>
         <v>15250.708910089512</v>
       </c>
-      <c r="V37" s="81">
+      <c r="V37">
         <f t="shared" si="181"/>
         <v>15221.896240112357</v>
       </c>
-      <c r="W37" s="81">
+      <c r="W37">
         <f t="shared" si="181"/>
         <v>15194.279919421642</v>
       </c>
-      <c r="X37" s="81">
+      <c r="X37">
         <f t="shared" si="181"/>
         <v>15167.532473271567</v>
       </c>
-      <c r="Y37" s="81">
+      <c r="Y37">
         <f t="shared" si="181"/>
         <v>15141.70607993106</v>
       </c>
-      <c r="Z37" s="81">
+      <c r="Z37">
         <f t="shared" si="181"/>
         <v>15116.869261943189</v>
       </c>
-      <c r="AA37" s="81">
+      <c r="AA37">
         <f t="shared" si="181"/>
         <v>15092.351872963813</v>
       </c>
-      <c r="AB37" s="81">
+      <c r="AB37">
         <f t="shared" si="181"/>
         <v>15068.971571339904</v>
       </c>
-      <c r="AC37" s="81">
+      <c r="AC37">
         <f t="shared" si="181"/>
         <v>15046.809166834548</v>
       </c>
-      <c r="AD37" s="81">
+      <c r="AD37">
         <f t="shared" si="181"/>
         <v>15025.93571491392</v>
       </c>
-      <c r="AE37" s="81">
+      <c r="AE37">
         <f t="shared" si="181"/>
         <v>15006.433316051523</v>
       </c>
-      <c r="AF37" s="81">
+      <c r="AF37">
         <f t="shared" si="181"/>
         <v>14987.169238631526</v>
       </c>
-      <c r="AG37" s="81">
+      <c r="AG37">
         <f t="shared" si="181"/>
         <v>14969.407679608492</v>
       </c>
-      <c r="AH37" s="81">
+      <c r="AH37">
         <f t="shared" si="181"/>
         <v>14953.21600605495</v>
       </c>
-      <c r="AI37" s="81">
+      <c r="AI37">
         <f t="shared" si="181"/>
         <v>14938.638750124421</v>
       </c>
-      <c r="AJ37" s="81">
+      <c r="AJ37">
         <f t="shared" si="181"/>
         <v>14925.728680348129</v>
       </c>
-      <c r="AK37" s="81">
+      <c r="AK37">
         <f t="shared" si="181"/>
         <v>14913.012428254826</v>
       </c>
-      <c r="AL37" s="81">
+      <c r="AL37">
         <f t="shared" si="181"/>
         <v>14902.197453446139</v>
       </c>
-      <c r="AM37" s="81">
+      <c r="AM37">
         <f t="shared" si="181"/>
         <v>14893.377776086205</v>
       </c>
-      <c r="AN37" s="81">
+      <c r="AN37">
         <f t="shared" si="181"/>
         <v>14886.649517233964</v>
       </c>
-      <c r="AO37" s="81">
+      <c r="AO37">
         <f t="shared" si="181"/>
         <v>14882.111220567127</v>
       </c>
-      <c r="AP37" s="81">
+      <c r="AP37">
         <f t="shared" si="181"/>
         <v>14878.770476658083</v>
       </c>
-      <c r="AQ37" s="81">
+      <c r="AQ37">
         <f>AQ43+AQ44</f>
         <v>14877.809725644393</v>
       </c>
-      <c r="AR37" s="81">
+      <c r="AR37">
         <f t="shared" ref="AR37:AT37" si="182">AR43+AR44</f>
         <v>14879.333857683061</v>
       </c>
-      <c r="AS37" s="81">
+      <c r="AS37">
         <f t="shared" si="182"/>
         <v>14883.450474555724</v>
       </c>
-      <c r="AT37" s="81">
+      <c r="AT37">
         <f t="shared" si="182"/>
         <v>14891.740640924232</v>
       </c>
     </row>
     <row r="38" spans="3:46">
-      <c r="D38" s="73" t="s">
+      <c r="D38" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E38" s="73">
+      <c r="E38" s="57">
         <f>E37/$E37</f>
         <v>1</v>
       </c>
-      <c r="F38" s="73">
+      <c r="F38" s="57">
         <f t="shared" ref="F38:O38" si="183">F37/$E37</f>
         <v>0.72638681616108225</v>
       </c>
-      <c r="G38" s="73">
+      <c r="G38" s="57">
         <f t="shared" si="183"/>
         <v>0.70959871205371039</v>
       </c>
-      <c r="H38" s="73">
+      <c r="H38" s="57">
         <f t="shared" si="183"/>
         <v>0.64426415785036162</v>
       </c>
-      <c r="I38" s="73">
+      <c r="I38" s="57">
         <f t="shared" si="183"/>
         <v>0.76400637311512787</v>
       </c>
-      <c r="J38" s="73">
+      <c r="J38" s="57">
         <f t="shared" si="183"/>
         <v>0.76112540281291752</v>
       </c>
-      <c r="K38" s="73">
+      <c r="K38" s="57">
         <f t="shared" si="183"/>
         <v>0.75782468436877115</v>
       </c>
-      <c r="L38" s="73">
+      <c r="L38" s="57">
         <f t="shared" si="183"/>
         <v>0.75462803352260688</v>
       </c>
-      <c r="M38" s="73">
+      <c r="M38" s="57">
         <f t="shared" si="183"/>
         <v>0.75201467523568954</v>
       </c>
-      <c r="N38" s="73">
+      <c r="N38" s="57">
         <f t="shared" si="183"/>
         <v>0.74978241667076462</v>
       </c>
-      <c r="O38" s="73">
+      <c r="O38" s="57">
         <f t="shared" si="183"/>
         <v>0.74781065381441392</v>
       </c>
-      <c r="P38" s="73">
+      <c r="P38" s="57">
         <f t="shared" ref="P38" si="184">P37/$E37</f>
         <v>0.74590712379009938</v>
       </c>
-      <c r="Q38" s="73">
+      <c r="Q38" s="57">
         <f t="shared" ref="Q38" si="185">Q37/$E37</f>
         <v>0.74412124742575536</v>
       </c>
-      <c r="R38" s="73">
+      <c r="R38" s="57">
         <f t="shared" ref="R38" si="186">R37/$E37</f>
         <v>0.74228341046450175</v>
       </c>
-      <c r="S38" s="73">
+      <c r="S38" s="57">
         <f t="shared" ref="S38" si="187">S37/$E37</f>
         <v>0.74046782072253237</v>
       </c>
-      <c r="T38" s="73">
+      <c r="T38" s="57">
         <f t="shared" ref="T38" si="188">T37/$E37</f>
         <v>0.73868146091580356</v>
       </c>
-      <c r="U38" s="73">
+      <c r="U38" s="57">
         <f t="shared" ref="U38" si="189">U37/$E37</f>
         <v>0.73733244555008315</v>
       </c>
-      <c r="V38" s="73">
+      <c r="V38" s="57">
         <f t="shared" ref="V38" si="190">V37/$E37</f>
         <v>0.7359394272620593</v>
       </c>
-      <c r="W38" s="73">
+      <c r="W38" s="57">
         <f t="shared" ref="W38" si="191">W37/$E37</f>
         <v>0.73460424937675406</v>
       </c>
-      <c r="X38" s="73">
+      <c r="X38" s="57">
         <f t="shared" ref="X38:Y38" si="192">X37/$E37</f>
         <v>0.73331107933473672</v>
       </c>
-      <c r="Y38" s="73">
+      <c r="Y38" s="57">
         <f t="shared" si="192"/>
         <v>0.73206243982074692</v>
       </c>
-      <c r="Z38" s="73">
+      <c r="Z38" s="57">
         <f t="shared" ref="Z38" si="193">Z37/$E37</f>
         <v>0.7308616437230282</v>
       </c>
-      <c r="AA38" s="73">
+      <c r="AA38" s="57">
         <f t="shared" ref="AA38" si="194">AA37/$E37</f>
         <v>0.72967629119409061</v>
       </c>
-      <c r="AB38" s="73">
+      <c r="AB38" s="57">
         <f t="shared" ref="AB38" si="195">AB37/$E37</f>
         <v>0.72854591390634038</v>
       </c>
-      <c r="AC38" s="73">
+      <c r="AC38" s="57">
         <f t="shared" ref="AC38" si="196">AC37/$E37</f>
         <v>0.72747441880342134</v>
       </c>
-      <c r="AD38" s="73">
+      <c r="AD38" s="57">
         <f t="shared" ref="AD38" si="197">AD37/$E37</f>
         <v>0.72646524123387723</v>
       </c>
-      <c r="AE38" s="73">
+      <c r="AE38" s="57">
         <f t="shared" ref="AE38" si="198">AE37/$E37</f>
         <v>0.72552235054387193</v>
       </c>
-      <c r="AF38" s="73">
+      <c r="AF38" s="57">
         <f t="shared" ref="AF38" si="199">AF37/$E37</f>
         <v>0.72459098208099637</v>
       </c>
-      <c r="AG38" s="73">
+      <c r="AG38" s="57">
         <f t="shared" ref="AG38" si="200">AG37/$E37</f>
         <v>0.72373225650774964</v>
       </c>
-      <c r="AH38" s="73">
+      <c r="AH38" s="57">
         <f t="shared" ref="AH38:AI38" si="201">AH37/$E37</f>
         <v>0.72294943084835472</v>
       </c>
-      <c r="AI38" s="73">
+      <c r="AI38" s="57">
         <f t="shared" si="201"/>
         <v>0.72224465811758964</v>
       </c>
-      <c r="AJ38" s="73">
+      <c r="AJ38" s="57">
         <f t="shared" ref="AJ38" si="202">AJ37/$E37</f>
         <v>0.72162048953785374</v>
       </c>
-      <c r="AK38" s="73">
+      <c r="AK38" s="57">
         <f t="shared" ref="AK38" si="203">AK37/$E37</f>
         <v>0.72100569154325145</v>
       </c>
-      <c r="AL38" s="73">
+      <c r="AL38" s="57">
         <f t="shared" ref="AL38" si="204">AL37/$E37</f>
         <v>0.72048281540213144</v>
       </c>
-      <c r="AM38" s="73">
+      <c r="AM38" s="57">
         <f t="shared" ref="AM38" si="205">AM37/$E37</f>
         <v>0.72005640674696003</v>
       </c>
-      <c r="AN38" s="73">
+      <c r="AN38" s="57">
         <f t="shared" ref="AN38" si="206">AN37/$E37</f>
         <v>0.71973111278304891</v>
       </c>
-      <c r="AO38" s="73">
+      <c r="AO38" s="57">
         <f t="shared" ref="AO38" si="207">AO37/$E37</f>
         <v>0.71951169784308</v>
       </c>
-      <c r="AP38" s="73">
+      <c r="AP38" s="57">
         <f t="shared" ref="AP38" si="208">AP37/$E37</f>
         <v>0.71935018149056595</v>
       </c>
-      <c r="AQ38" s="73">
+      <c r="AQ38" s="57">
         <f>AQ37/$E37</f>
         <v>0.71930373165674732</v>
       </c>
-      <c r="AR38" s="73">
+      <c r="AR38" s="57">
         <f t="shared" ref="AR38" si="209">AR37/$E37</f>
         <v>0.71937741951021295</v>
       </c>
-      <c r="AS38" s="73">
+      <c r="AS38" s="57">
         <f t="shared" ref="AS38" si="210">AS37/$E37</f>
         <v>0.71957644731960901</v>
       </c>
-      <c r="AT38" s="73">
+      <c r="AT38" s="57">
         <f t="shared" ref="AT38" si="211">AT37/$E37</f>
         <v>0.7199772554839079</v>
       </c>
@@ -11864,144 +11863,144 @@
   <sheetFormatPr defaultRowHeight="12.9"/>
   <sheetData>
     <row r="1" spans="1:16" ht="59.8">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75" t="s">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="J1" s="75" t="s">
+      <c r="J1" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="75" t="s">
+      <c r="K1" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="75" t="s">
+      <c r="M1" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="P1" s="80" t="s">
+      <c r="P1" s="64" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="14.3">
-      <c r="A2" s="76">
+      <c r="A2" s="60">
         <v>2020</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="F2" s="76">
+      <c r="F2" s="60">
         <v>442</v>
       </c>
-      <c r="G2" s="76">
+      <c r="G2" s="60">
         <v>176</v>
       </c>
-      <c r="H2" s="76">
+      <c r="H2" s="60">
         <v>320</v>
       </c>
-      <c r="I2" s="76">
+      <c r="I2" s="60">
         <v>379</v>
       </c>
-      <c r="J2" s="76">
+      <c r="J2" s="60">
         <v>249</v>
       </c>
-      <c r="K2" s="78">
+      <c r="K2" s="62">
         <v>30515</v>
       </c>
-      <c r="L2" s="78">
+      <c r="L2" s="62">
         <v>83282</v>
       </c>
-      <c r="M2" s="79">
+      <c r="M2" s="63">
         <v>16764</v>
       </c>
-      <c r="N2" s="79">
+      <c r="N2" s="63">
         <v>34036</v>
       </c>
-      <c r="O2" s="79">
+      <c r="O2" s="63">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="14.3">
-      <c r="A3" s="76">
+      <c r="A3" s="60">
         <v>2025</v>
       </c>
-      <c r="B3" s="76">
+      <c r="B3" s="60">
         <v>19740</v>
       </c>
-      <c r="C3" s="76">
+      <c r="C3" s="60">
         <v>8515</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="60">
         <v>90</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="60">
         <v>14626</v>
       </c>
-      <c r="F3" s="76">
+      <c r="F3" s="60">
         <v>676</v>
       </c>
-      <c r="G3" s="76">
+      <c r="G3" s="60">
         <v>357</v>
       </c>
-      <c r="H3" s="76">
+      <c r="H3" s="60">
         <v>304</v>
       </c>
-      <c r="I3" s="76">
+      <c r="I3" s="60">
         <v>409</v>
       </c>
-      <c r="J3" s="76">
+      <c r="J3" s="60">
         <v>1664</v>
       </c>
-      <c r="K3" s="79">
+      <c r="K3" s="63">
         <v>38622</v>
       </c>
-      <c r="L3" s="79">
+      <c r="L3" s="63">
         <v>93599</v>
       </c>
-      <c r="M3" s="79">
+      <c r="M3" s="63">
         <v>19278</v>
       </c>
-      <c r="N3" s="79">
+      <c r="N3" s="63">
         <v>37672</v>
       </c>
-      <c r="O3" s="79">
+      <c r="O3" s="63">
         <v>95</v>
       </c>
       <c r="P3">
@@ -12009,49 +12008,49 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="14.3">
-      <c r="A4" s="76">
+      <c r="A4" s="60">
         <v>2030</v>
       </c>
-      <c r="B4" s="76">
+      <c r="B4" s="60">
         <v>26143</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="60">
         <v>8467</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="60">
         <v>98</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="60">
         <v>19544</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="60">
         <v>670</v>
       </c>
-      <c r="G4" s="76">
+      <c r="G4" s="60">
         <v>591</v>
       </c>
-      <c r="H4" s="76">
+      <c r="H4" s="60">
         <v>289</v>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="60">
         <v>429</v>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="60">
         <v>2393</v>
       </c>
-      <c r="K4" s="79">
+      <c r="K4" s="63">
         <v>41810</v>
       </c>
-      <c r="L4" s="79">
+      <c r="L4" s="63">
         <v>109910</v>
       </c>
-      <c r="M4" s="79">
+      <c r="M4" s="63">
         <v>21364</v>
       </c>
-      <c r="N4" s="79">
+      <c r="N4" s="63">
         <v>41580</v>
       </c>
-      <c r="O4" s="79">
+      <c r="O4" s="63">
         <v>112</v>
       </c>
       <c r="P4">
@@ -12059,49 +12058,49 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.3">
-      <c r="A5" s="76">
+      <c r="A5" s="60">
         <v>2035</v>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="60">
         <v>32149</v>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="60">
         <v>7079</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="60">
         <v>97</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="60">
         <v>24101</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="60">
         <v>644</v>
       </c>
-      <c r="G5" s="76">
+      <c r="G5" s="60">
         <v>920</v>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="60">
         <v>266</v>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="60">
         <v>447</v>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="60">
         <v>2724</v>
       </c>
-      <c r="K5" s="79">
+      <c r="K5" s="63">
         <v>44461</v>
       </c>
-      <c r="L5" s="79">
+      <c r="L5" s="63">
         <v>127932</v>
       </c>
-      <c r="M5" s="79">
+      <c r="M5" s="63">
         <v>23726</v>
       </c>
-      <c r="N5" s="79">
+      <c r="N5" s="63">
         <v>45505</v>
       </c>
-      <c r="O5" s="79">
+      <c r="O5" s="63">
         <v>127</v>
       </c>
       <c r="P5">
@@ -12109,49 +12108,49 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="14.3">
-      <c r="A6" s="76">
+      <c r="A6" s="60">
         <v>2040</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="60">
         <v>39395</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="60">
         <v>8496</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="60">
         <v>89</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="60">
         <v>24496</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="60">
         <v>606</v>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="60">
         <v>1117</v>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="60">
         <v>239</v>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="60">
         <v>461</v>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="60">
         <v>3337</v>
       </c>
-      <c r="K6" s="79">
+      <c r="K6" s="63">
         <v>48066</v>
       </c>
-      <c r="L6" s="79">
+      <c r="L6" s="63">
         <v>143831</v>
       </c>
-      <c r="M6" s="79">
+      <c r="M6" s="63">
         <v>26279</v>
       </c>
-      <c r="N6" s="79">
+      <c r="N6" s="63">
         <v>49367</v>
       </c>
-      <c r="O6" s="79">
+      <c r="O6" s="63">
         <v>139</v>
       </c>
       <c r="P6">
@@ -12159,49 +12158,49 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="14.3">
-      <c r="A7" s="76">
+      <c r="A7" s="60">
         <v>2045</v>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="60">
         <v>47081</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="60">
         <v>8035</v>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="60">
         <v>76</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="60">
         <v>25144</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="60">
         <v>551</v>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="60">
         <v>1133</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="60">
         <v>227</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="60">
         <v>472</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="60">
         <v>4062</v>
       </c>
-      <c r="K7" s="79">
+      <c r="K7" s="63">
         <v>49671</v>
       </c>
-      <c r="L7" s="79">
+      <c r="L7" s="63">
         <v>162610</v>
       </c>
-      <c r="M7" s="79">
+      <c r="M7" s="63">
         <v>26388</v>
       </c>
-      <c r="N7" s="79">
+      <c r="N7" s="63">
         <v>50374</v>
       </c>
-      <c r="O7" s="79">
+      <c r="O7" s="63">
         <v>143</v>
       </c>
       <c r="P7">
@@ -12209,49 +12208,49 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.3">
-      <c r="A8" s="76">
+      <c r="A8" s="60">
         <v>2050</v>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="60">
         <v>53109</v>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="60">
         <v>6996</v>
       </c>
-      <c r="D8" s="76">
+      <c r="D8" s="60">
         <v>56</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="60">
         <v>24333</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="60">
         <v>498</v>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="60">
         <v>1091</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="60">
         <v>215</v>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="60">
         <v>484</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="60">
         <v>4585</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="63">
         <v>51277</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="63">
         <v>181928</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="63">
         <v>26498</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="63">
         <v>51381</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="63">
         <v>146</v>
       </c>
       <c r="P8">
@@ -12259,49 +12258,49 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.3">
-      <c r="A9" s="76">
+      <c r="A9" s="60">
         <v>2055</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="60">
         <v>60948</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="60">
         <v>4853</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="60">
         <v>48</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="60">
         <v>21714</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="60">
         <v>412</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="60">
         <v>989</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="60">
         <v>194</v>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="60">
         <v>489</v>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="60">
         <v>4790</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="63">
         <v>53097</v>
       </c>
-      <c r="L9" s="79">
+      <c r="L9" s="63">
         <v>197391</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="63">
         <v>26625</v>
       </c>
-      <c r="N9" s="79">
+      <c r="N9" s="63">
         <v>51704</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="63">
         <v>148</v>
       </c>
       <c r="P9">
@@ -12309,49 +12308,49 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.3">
-      <c r="A10" s="76">
+      <c r="A10" s="60">
         <v>2060</v>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="60">
         <v>67849</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="60">
         <v>2481</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="60">
         <v>48</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="60">
         <v>18482</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="60">
         <v>332</v>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="60">
         <v>901</v>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="60">
         <v>172</v>
       </c>
-      <c r="I10" s="76">
+      <c r="I10" s="60">
         <v>494</v>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="60">
         <v>4720</v>
       </c>
-      <c r="K10" s="79">
+      <c r="K10" s="63">
         <v>54917</v>
       </c>
-      <c r="L10" s="79">
+      <c r="L10" s="63">
         <v>204943</v>
       </c>
-      <c r="M10" s="79">
+      <c r="M10" s="63">
         <v>26752</v>
       </c>
-      <c r="N10" s="79">
+      <c r="N10" s="63">
         <v>52026</v>
       </c>
-      <c r="O10" s="79">
+      <c r="O10" s="63">
         <v>150</v>
       </c>
       <c r="P10">
@@ -12380,11 +12379,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="14.95" thickBot="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
       <c r="D1" s="22" t="s">
         <v>27</v>
       </c>
@@ -12609,11 +12608,11 @@
       </c>
     </row>
     <row r="2" spans="1:77" ht="15.65" customHeight="1" thickBot="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="64"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="72"/>
       <c r="D2" s="13">
         <v>9928</v>
       </c>
@@ -12724,11 +12723,11 @@
       </c>
     </row>
     <row r="3" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
       <c r="D3" s="9">
         <v>5345.19</v>
       </c>
@@ -12989,11 +12988,11 @@
       </c>
     </row>
     <row r="4" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="9">
         <v>350.3</v>
       </c>
@@ -13254,11 +13253,11 @@
       </c>
     </row>
     <row r="5" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="9">
         <v>3801.8</v>
       </c>
@@ -13520,10 +13519,10 @@
     </row>
     <row r="6" spans="1:77" ht="16.3" thickBot="1">
       <c r="A6" s="27"/>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="64"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="14">
         <v>2487</v>
       </c>
@@ -16887,175 +16886,175 @@
       </c>
     </row>
     <row r="32" spans="1:77">
-      <c r="D32" s="73" t="s">
+      <c r="D32" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="73">
-        <f>E31/$E$31</f>
+      <c r="E32" s="57">
+        <f t="shared" ref="E32:J32" si="29">E31/$E$31</f>
         <v>1</v>
       </c>
-      <c r="F32" s="73">
-        <f>F31/$E$31</f>
+      <c r="F32" s="57">
+        <f t="shared" si="29"/>
         <v>0.91261398176291797</v>
       </c>
-      <c r="G32" s="73">
-        <f>G31/$E$31</f>
+      <c r="G32" s="57">
+        <f t="shared" si="29"/>
         <v>1.0568389057750762</v>
       </c>
-      <c r="H32" s="73">
-        <f>H31/$E$31</f>
+      <c r="H32" s="57">
+        <f t="shared" si="29"/>
         <v>0.96542553191489366</v>
       </c>
-      <c r="I32" s="73">
-        <f>I31/$E$31</f>
+      <c r="I32" s="57">
+        <f t="shared" si="29"/>
         <v>1.0775835866261398</v>
       </c>
-      <c r="J32" s="73">
-        <f>J31/$E$31</f>
+      <c r="J32" s="57">
+        <f t="shared" si="29"/>
         <v>1.3445668693009118</v>
       </c>
-      <c r="K32" s="73">
+      <c r="K32" s="57">
         <f>(1+K33)*J32/$E$32</f>
         <v>1.3984176791404332</v>
       </c>
-      <c r="L32" s="73">
-        <f t="shared" ref="L32:AT32" si="29">(1+L33)*K32/$E$32</f>
+      <c r="L32" s="57">
+        <f t="shared" ref="L32:AT32" si="30">(1+L33)*K32/$E$32</f>
         <v>1.4529251443088298</v>
       </c>
-      <c r="M32" s="73">
-        <f t="shared" si="29"/>
+      <c r="M32" s="57">
+        <f t="shared" si="30"/>
         <v>1.4994441506473171</v>
       </c>
-      <c r="N32" s="73">
-        <f t="shared" si="29"/>
+      <c r="N32" s="57">
+        <f t="shared" si="30"/>
         <v>1.5406118957354304</v>
       </c>
-      <c r="O32" s="73">
-        <f t="shared" si="29"/>
+      <c r="O32" s="57">
+        <f t="shared" si="30"/>
         <v>1.5780989933025782</v>
       </c>
-      <c r="P32" s="73">
-        <f t="shared" si="29"/>
+      <c r="P32" s="57">
+        <f t="shared" si="30"/>
         <v>1.6152793551582547</v>
       </c>
-      <c r="Q32" s="73">
-        <f t="shared" si="29"/>
+      <c r="Q32" s="57">
+        <f t="shared" si="30"/>
         <v>1.6510859577662245</v>
       </c>
-      <c r="R32" s="73">
-        <f t="shared" si="29"/>
+      <c r="R32" s="57">
+        <f t="shared" si="30"/>
         <v>1.6888528402657748</v>
       </c>
-      <c r="S32" s="73">
-        <f t="shared" si="29"/>
+      <c r="S32" s="57">
+        <f t="shared" si="30"/>
         <v>1.7271222145467906</v>
       </c>
-      <c r="T32" s="73">
-        <f t="shared" si="29"/>
+      <c r="T32" s="57">
+        <f t="shared" si="30"/>
         <v>1.7657348550500753</v>
       </c>
-      <c r="U32" s="73">
-        <f t="shared" si="29"/>
+      <c r="U32" s="57">
+        <f t="shared" si="30"/>
         <v>1.8039598821254301</v>
       </c>
-      <c r="V32" s="73">
-        <f t="shared" si="29"/>
+      <c r="V32" s="57">
+        <f t="shared" si="30"/>
         <v>1.8443894253187751</v>
       </c>
-      <c r="W32" s="73">
-        <f t="shared" si="29"/>
+      <c r="W32" s="57">
+        <f t="shared" si="30"/>
         <v>1.8841136199395006</v>
       </c>
-      <c r="X32" s="73">
-        <f t="shared" si="29"/>
+      <c r="X32" s="57">
+        <f t="shared" si="30"/>
         <v>1.9235165719601217</v>
       </c>
-      <c r="Y32" s="73">
-        <f t="shared" si="29"/>
+      <c r="Y32" s="57">
+        <f t="shared" si="30"/>
         <v>1.9624541614497415</v>
       </c>
-      <c r="Z32" s="73">
-        <f t="shared" si="29"/>
+      <c r="Z32" s="57">
+        <f t="shared" si="30"/>
         <v>2.0007489709435924</v>
       </c>
-      <c r="AA32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AA32" s="57">
+        <f t="shared" si="30"/>
         <v>2.0393775226920829</v>
       </c>
-      <c r="AB32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AB32" s="57">
+        <f t="shared" si="30"/>
         <v>2.0770110905861077</v>
       </c>
-      <c r="AC32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AC32" s="57">
+        <f t="shared" si="30"/>
         <v>2.1134214730578313</v>
       </c>
-      <c r="AD32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AD32" s="57">
+        <f t="shared" si="30"/>
         <v>2.1483873310415347</v>
       </c>
-      <c r="AE32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AE32" s="57">
+        <f t="shared" si="30"/>
         <v>2.1816615540060962</v>
       </c>
-      <c r="AF32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AF32" s="57">
+        <f t="shared" si="30"/>
         <v>2.2150989241955128</v>
       </c>
-      <c r="AG32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AG32" s="57">
+        <f t="shared" si="30"/>
         <v>2.2464571415849068</v>
       </c>
-      <c r="AH32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AH32" s="57">
+        <f t="shared" si="30"/>
         <v>2.2754965466913193</v>
       </c>
-      <c r="AI32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AI32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3020186253936443</v>
       </c>
-      <c r="AJ32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AJ32" s="57">
+        <f t="shared" si="30"/>
         <v>2.325813632347574</v>
       </c>
-      <c r="AK32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AK32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3495223448300533</v>
       </c>
-      <c r="AL32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AL32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3699160960534305</v>
       </c>
-      <c r="AM32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AM32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3867087247538286</v>
       </c>
-      <c r="AN32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AN32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3996207689142492</v>
       </c>
-      <c r="AO32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AO32" s="57">
+        <f t="shared" si="30"/>
         <v>2.4083827652373375</v>
       </c>
-      <c r="AP32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AP32" s="57">
+        <f t="shared" si="30"/>
         <v>2.4148589855453437</v>
       </c>
-      <c r="AQ32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AQ32" s="57">
+        <f t="shared" si="30"/>
         <v>2.4167270506965299</v>
       </c>
-      <c r="AR32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AR32" s="57">
+        <f t="shared" si="30"/>
         <v>2.413760998151631</v>
       </c>
-      <c r="AS32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AS32" s="57">
+        <f t="shared" si="30"/>
         <v>2.4057607935759342</v>
       </c>
-      <c r="AT32" s="73">
-        <f t="shared" si="29"/>
+      <c r="AT32" s="57">
+        <f t="shared" si="30"/>
         <v>2.3897093564136922</v>
       </c>
     </row>
@@ -17205,15 +17204,15 @@
         <v>39239.533996977785</v>
       </c>
       <c r="M34">
-        <f t="shared" ref="M34:O36" si="30">($P34/$K34)^(0.2)*L34</f>
+        <f t="shared" ref="M34:O36" si="31">($P34/$K34)^(0.2)*L34</f>
         <v>39866.94185438288</v>
       </c>
       <c r="N34">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>40504.381447118059</v>
       </c>
       <c r="O34">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>41152.013174375883</v>
       </c>
       <c r="P34">
@@ -17224,18 +17223,18 @@
         <v>42327.242791662262</v>
       </c>
       <c r="R34">
-        <f t="shared" ref="R34:T36" si="31">($U34/$P34)^(0.2)*Q34</f>
+        <f t="shared" ref="R34:T36" si="32">($U34/$P34)^(0.2)*Q34</f>
         <v>42850.88453346867</v>
       </c>
       <c r="S34">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>43381.004388558089</v>
       </c>
       <c r="T34">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>43917.682499417948</v>
       </c>
-      <c r="U34" s="79">
+      <c r="U34" s="63">
         <v>44461</v>
       </c>
       <c r="V34">
@@ -17243,18 +17242,18 @@
         <v>45159.692657414722</v>
       </c>
       <c r="W34">
-        <f t="shared" ref="W34:Y36" si="32">($Z34/$U34)^(0.2)*V34</f>
+        <f t="shared" ref="W34:Y36" si="33">($Z34/$U34)^(0.2)*V34</f>
         <v>45869.365082030476</v>
       </c>
       <c r="X34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46590.189817935869</v>
       </c>
       <c r="Y34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>47322.342120703455</v>
       </c>
-      <c r="Z34" s="79">
+      <c r="Z34" s="63">
         <v>48066</v>
       </c>
       <c r="AA34">
@@ -17262,18 +17261,18 @@
         <v>48382.796461540631</v>
       </c>
       <c r="AB34">
-        <f t="shared" ref="AB34:AD36" si="33">($AE34/$Z34)^(0.2)*AA34</f>
+        <f t="shared" ref="AB34:AD36" si="34">($AE34/$Z34)^(0.2)*AA34</f>
         <v>48701.680885425638</v>
       </c>
       <c r="AC34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>49022.667033130543</v>
       </c>
       <c r="AD34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>49345.768756830883</v>
       </c>
-      <c r="AE34" s="79">
+      <c r="AE34" s="63">
         <v>49671</v>
       </c>
       <c r="AF34">
@@ -17281,18 +17280,18 @@
         <v>49988.124696397652</v>
       </c>
       <c r="AG34">
-        <f t="shared" ref="AG34:AI36" si="34">($AJ34/$AE34)^(0.2)*AF34</f>
+        <f t="shared" ref="AG34:AI36" si="35">($AJ34/$AE34)^(0.2)*AF34</f>
         <v>50307.274076676549</v>
       </c>
       <c r="AH34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>50628.461067438955</v>
       </c>
       <c r="AI34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>50951.698677817083</v>
       </c>
-      <c r="AJ34" s="79">
+      <c r="AJ34" s="63">
         <v>51277</v>
       </c>
       <c r="AK34">
@@ -17300,18 +17299,18 @@
         <v>51635.939539426283</v>
       </c>
       <c r="AL34">
-        <f t="shared" ref="AL34:AN36" si="35">($AO34/$AJ34)^(0.2)*AK34</f>
+        <f t="shared" ref="AL34:AN36" si="36">($AO34/$AJ34)^(0.2)*AK34</f>
         <v>51997.391659404537</v>
       </c>
       <c r="AM34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>52361.373948025059</v>
       </c>
       <c r="AN34">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>52727.904116494967</v>
       </c>
-      <c r="AO34" s="79">
+      <c r="AO34" s="63">
         <v>53097</v>
       </c>
       <c r="AP34">
@@ -17319,191 +17318,191 @@
         <v>53456.10952433286</v>
       </c>
       <c r="AQ34">
-        <f t="shared" ref="AQ34:AS36" si="36">($AT34/$AO34)^(0.2)*AP34</f>
+        <f t="shared" ref="AQ34:AS36" si="37">($AT34/$AO34)^(0.2)*AP34</f>
         <v>53817.64780453642</v>
       </c>
       <c r="AR34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>54181.631266950499</v>
       </c>
       <c r="AS34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>54548.076449010747</v>
       </c>
-      <c r="AT34" s="79">
+      <c r="AT34" s="63">
         <v>54917</v>
       </c>
     </row>
     <row r="35" spans="3:46">
-      <c r="D35" s="73" t="s">
+      <c r="D35" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E35" s="73">
+      <c r="E35" s="57">
         <f>E34/$E$34</f>
         <v>1</v>
       </c>
-      <c r="F35" s="73">
-        <f t="shared" ref="F35:S35" si="37">F34/$E$34</f>
+      <c r="F35" s="57">
+        <f t="shared" ref="F35:S35" si="38">F34/$E$34</f>
         <v>1.011016499900603</v>
       </c>
-      <c r="G35" s="73">
-        <f t="shared" si="37"/>
+      <c r="G35" s="57">
+        <f t="shared" si="38"/>
         <v>1.1012524020939634</v>
       </c>
-      <c r="H35" s="73">
-        <f t="shared" si="37"/>
+      <c r="H35" s="57">
+        <f t="shared" si="38"/>
         <v>1.1909648134649791</v>
       </c>
-      <c r="I35" s="73">
-        <f t="shared" si="37"/>
+      <c r="I35" s="57">
+        <f t="shared" si="38"/>
         <v>1.2080180239878073</v>
       </c>
-      <c r="J35" s="73">
-        <f t="shared" si="37"/>
+      <c r="J35" s="57">
+        <f t="shared" si="38"/>
         <v>1.1881883241667219</v>
       </c>
-      <c r="K35" s="73">
-        <f t="shared" si="37"/>
+      <c r="K35" s="57">
+        <f t="shared" si="38"/>
         <v>1.2796368696574116</v>
       </c>
-      <c r="L35" s="73">
+      <c r="L35" s="57">
         <f>L34/$E$34</f>
         <v>1.3000972101576365</v>
       </c>
-      <c r="M35" s="73">
-        <f t="shared" si="37"/>
+      <c r="M35" s="57">
+        <f t="shared" si="38"/>
         <v>1.3208846946651276</v>
       </c>
-      <c r="N35" s="73">
-        <f t="shared" si="37"/>
+      <c r="N35" s="57">
+        <f t="shared" si="38"/>
         <v>1.3420045539433456</v>
       </c>
-      <c r="O35" s="73">
-        <f t="shared" si="37"/>
+      <c r="O35" s="57">
+        <f t="shared" si="38"/>
         <v>1.3634621023913551</v>
       </c>
-      <c r="P35" s="73">
-        <f t="shared" si="37"/>
+      <c r="P35" s="57">
+        <f t="shared" si="38"/>
         <v>1.3852627393810881</v>
       </c>
-      <c r="Q35" s="73">
-        <f t="shared" si="37"/>
+      <c r="Q35" s="57">
+        <f t="shared" si="38"/>
         <v>1.4024001985177346</v>
       </c>
-      <c r="R35" s="73">
-        <f t="shared" si="37"/>
+      <c r="R35" s="57">
+        <f t="shared" si="38"/>
         <v>1.4197496697855898</v>
       </c>
-      <c r="S35" s="73">
-        <f t="shared" si="37"/>
+      <c r="S35" s="57">
+        <f t="shared" si="38"/>
         <v>1.4373137760439365</v>
       </c>
-      <c r="T35" s="73">
-        <f t="shared" ref="T35" si="38">T34/$E$34</f>
+      <c r="T35" s="57">
+        <f t="shared" ref="T35" si="39">T34/$E$34</f>
         <v>1.4550951726001573</v>
       </c>
-      <c r="U35" s="73">
-        <f t="shared" ref="U35" si="39">U34/$E$34</f>
+      <c r="U35" s="57">
+        <f t="shared" ref="U35" si="40">U34/$E$34</f>
         <v>1.473096547611159</v>
       </c>
-      <c r="V35" s="73">
-        <f t="shared" ref="V35" si="40">V34/$E$34</f>
+      <c r="V35" s="57">
+        <f t="shared" ref="V35" si="41">V34/$E$34</f>
         <v>1.4962458636742006</v>
       </c>
-      <c r="W35" s="73">
-        <f t="shared" ref="W35" si="41">W34/$E$34</f>
+      <c r="W35" s="57">
+        <f t="shared" ref="W35" si="42">W34/$E$34</f>
         <v>1.5197589650132688</v>
       </c>
-      <c r="X35" s="73">
-        <f t="shared" ref="X35" si="42">X34/$E$34</f>
+      <c r="X35" s="57">
+        <f t="shared" ref="X35" si="43">X34/$E$34</f>
         <v>1.5436415684161378</v>
       </c>
-      <c r="Y35" s="73">
-        <f t="shared" ref="Y35" si="43">Y34/$E$34</f>
+      <c r="Y35" s="57">
+        <f t="shared" ref="Y35" si="44">Y34/$E$34</f>
         <v>1.5678994805083644</v>
       </c>
-      <c r="Z35" s="73">
-        <f t="shared" ref="Z35" si="44">Z34/$E$34</f>
+      <c r="Z35" s="57">
+        <f t="shared" ref="Z35" si="45">Z34/$E$34</f>
         <v>1.5925385991650653</v>
       </c>
-      <c r="AA35" s="73">
-        <f t="shared" ref="AA35" si="45">AA34/$E$34</f>
+      <c r="AA35" s="57">
+        <f t="shared" ref="AA35" si="46">AA34/$E$34</f>
         <v>1.6030348042389713</v>
       </c>
-      <c r="AB35" s="73">
-        <f t="shared" ref="AB35" si="46">AB34/$E$34</f>
+      <c r="AB35" s="57">
+        <f t="shared" ref="AB35" si="47">AB34/$E$34</f>
         <v>1.6136001883714015</v>
       </c>
-      <c r="AC35" s="73">
-        <f t="shared" ref="AC35" si="47">AC34/$E$34</f>
+      <c r="AC35" s="57">
+        <f t="shared" ref="AC35" si="48">AC34/$E$34</f>
         <v>1.6242352075121114</v>
       </c>
-      <c r="AD35" s="73">
-        <f t="shared" ref="AD35" si="48">AD34/$E$34</f>
+      <c r="AD35" s="57">
+        <f t="shared" ref="AD35" si="49">AD34/$E$34</f>
         <v>1.6349403206159592</v>
       </c>
-      <c r="AE35" s="73">
-        <f t="shared" ref="AE35" si="49">AE34/$E$34</f>
+      <c r="AE35" s="57">
+        <f t="shared" ref="AE35" si="50">AE34/$E$34</f>
         <v>1.6457159896627129</v>
       </c>
-      <c r="AF35" s="73">
-        <f t="shared" ref="AF35" si="50">AF34/$E$34</f>
+      <c r="AF35" s="57">
+        <f t="shared" ref="AF35" si="51">AF34/$E$34</f>
         <v>1.6562230699223925</v>
       </c>
-      <c r="AG35" s="73">
-        <f t="shared" ref="AG35" si="51">AG34/$E$34</f>
+      <c r="AG35" s="57">
+        <f t="shared" ref="AG35" si="52">AG34/$E$34</f>
         <v>1.6667972326776406</v>
       </c>
-      <c r="AH35" s="73">
-        <f t="shared" ref="AH35" si="52">AH34/$E$34</f>
+      <c r="AH35" s="57">
+        <f t="shared" ref="AH35" si="53">AH34/$E$34</f>
         <v>1.6774389062169159</v>
       </c>
-      <c r="AI35" s="73">
-        <f t="shared" ref="AI35" si="53">AI34/$E$34</f>
+      <c r="AI35" s="57">
+        <f t="shared" ref="AI35" si="54">AI34/$E$34</f>
         <v>1.6881485215630867</v>
       </c>
-      <c r="AJ35" s="73">
-        <f t="shared" ref="AJ35" si="54">AJ34/$E$34</f>
+      <c r="AJ35" s="57">
+        <f t="shared" ref="AJ35" si="55">AJ34/$E$34</f>
         <v>1.6989265124908886</v>
       </c>
-      <c r="AK35" s="73">
-        <f t="shared" ref="AK35" si="55">AK34/$E$34</f>
+      <c r="AK35" s="57">
+        <f t="shared" ref="AK35" si="56">AK34/$E$34</f>
         <v>1.7108190159507748</v>
       </c>
-      <c r="AL35" s="73">
-        <f t="shared" ref="AL35" si="56">AL34/$E$34</f>
+      <c r="AL35" s="57">
+        <f t="shared" ref="AL35" si="57">AL34/$E$34</f>
         <v>1.7227947670599872</v>
       </c>
-      <c r="AM35" s="73">
-        <f t="shared" ref="AM35" si="57">AM34/$E$34</f>
+      <c r="AM35" s="57">
+        <f t="shared" ref="AM35" si="58">AM34/$E$34</f>
         <v>1.7348543485529475</v>
       </c>
-      <c r="AN35" s="73">
-        <f t="shared" ref="AN35" si="58">AN34/$E$34</f>
+      <c r="AN35" s="57">
+        <f t="shared" ref="AN35" si="59">AN34/$E$34</f>
         <v>1.7469983472432233</v>
       </c>
-      <c r="AO35" s="73">
-        <f t="shared" ref="AO35" si="59">AO34/$E$34</f>
+      <c r="AO35" s="57">
+        <f t="shared" ref="AO35" si="60">AO34/$E$34</f>
         <v>1.759227354052084</v>
       </c>
-      <c r="AP35" s="73">
-        <f t="shared" ref="AP35" si="60">AP34/$E$34</f>
+      <c r="AP35" s="57">
+        <f t="shared" ref="AP35" si="61">AP34/$E$34</f>
         <v>1.7711254895080797</v>
       </c>
-      <c r="AQ35" s="73">
-        <f t="shared" ref="AQ35" si="61">AQ34/$E$34</f>
+      <c r="AQ35" s="57">
+        <f t="shared" ref="AQ35" si="62">AQ34/$E$34</f>
         <v>1.7831040953063555</v>
       </c>
-      <c r="AR35" s="73">
-        <f t="shared" ref="AR35" si="62">AR34/$E$34</f>
+      <c r="AR35" s="57">
+        <f t="shared" ref="AR35" si="63">AR34/$E$34</f>
         <v>1.7951637156898317</v>
       </c>
-      <c r="AS35" s="73">
-        <f t="shared" ref="AS35" si="63">AS34/$E$34</f>
+      <c r="AS35" s="57">
+        <f t="shared" ref="AS35" si="64">AS34/$E$34</f>
         <v>1.8073048985822924</v>
       </c>
-      <c r="AT35" s="73">
-        <f t="shared" ref="AT35" si="64">AT34/$E$34</f>
+      <c r="AT35" s="57">
+        <f t="shared" ref="AT35" si="65">AT34/$E$34</f>
         <v>1.8195281956132794</v>
       </c>
     </row>
@@ -17541,15 +17540,15 @@
         <v>147687.70188149178</v>
       </c>
       <c r="M36">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>150364.21382030798</v>
       </c>
       <c r="N36">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>153089.23159994482</v>
       </c>
       <c r="O36">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>155863.63428115277</v>
       </c>
       <c r="P36">
@@ -17561,15 +17560,15 @@
         <v>160887.3113107353</v>
       </c>
       <c r="R36">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>163116.77793100459</v>
       </c>
       <c r="S36">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>165377.13897899725</v>
       </c>
       <c r="T36">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>167668.82256861983</v>
       </c>
       <c r="U36">
@@ -17581,15 +17580,15 @@
         <v>172140.47773565742</v>
       </c>
       <c r="W36">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>174315.840005531</v>
       </c>
       <c r="X36">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>176518.69261972938</v>
       </c>
       <c r="Y36">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>178749.38297741525</v>
       </c>
       <c r="Z36">
@@ -17601,15 +17600,15 @@
         <v>181998.95341207349</v>
       </c>
       <c r="AB36">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>182995.06618251573</v>
       </c>
       <c r="AC36">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>183996.63085602026</v>
       </c>
       <c r="AD36">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>185003.67727182605</v>
       </c>
       <c r="AE36">
@@ -17621,15 +17620,15 @@
         <v>186932.17529725743</v>
       </c>
       <c r="AG36">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>187852.62522983906</v>
       </c>
       <c r="AH36">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>188777.6074377074</v>
       </c>
       <c r="AI36">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>189707.14423768659</v>
       </c>
       <c r="AJ36">
@@ -17641,15 +17640,15 @@
         <v>190972.37824021498</v>
       </c>
       <c r="AL36">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>191304.07353856898</v>
       </c>
       <c r="AM36">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>191636.34495045294</v>
       </c>
       <c r="AN36">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>191969.19347650447</v>
       </c>
       <c r="AO36">
@@ -17661,15 +17660,15 @@
         <v>192633.55157726113</v>
       </c>
       <c r="AQ36">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>192965.05253171973</v>
       </c>
       <c r="AR36">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>193297.12396251492</v>
       </c>
       <c r="AS36">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>193629.7668513731</v>
       </c>
       <c r="AT36">
@@ -17678,175 +17677,175 @@
       </c>
     </row>
     <row r="37" spans="3:46">
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E37" s="73">
+      <c r="E37" s="57">
         <f>E36/$E36</f>
         <v>1</v>
       </c>
-      <c r="F37" s="73">
-        <f t="shared" ref="F37:J37" si="65">F36/$E36</f>
+      <c r="F37" s="57">
+        <f t="shared" ref="F37:J37" si="66">F36/$E36</f>
         <v>1.0180006348412416</v>
       </c>
-      <c r="G37" s="73">
-        <f t="shared" si="65"/>
+      <c r="G37" s="57">
+        <f t="shared" si="66"/>
         <v>1.1117176303107836</v>
       </c>
-      <c r="H37" s="73">
-        <f t="shared" si="65"/>
+      <c r="H37" s="57">
+        <f t="shared" si="66"/>
         <v>1.1639054278926158</v>
       </c>
-      <c r="I37" s="73">
-        <f t="shared" si="65"/>
+      <c r="I37" s="57">
+        <f t="shared" si="66"/>
         <v>1.2499783576849457</v>
       </c>
-      <c r="J37" s="73">
-        <f t="shared" si="65"/>
+      <c r="J37" s="57">
+        <f t="shared" si="66"/>
         <v>1.3603195367582697</v>
       </c>
-      <c r="K37" s="73">
-        <f t="shared" ref="K37" si="66">K36/$E36</f>
+      <c r="K37" s="57">
+        <f t="shared" ref="K37" si="67">K36/$E36</f>
         <v>1.3952928673681615</v>
       </c>
-      <c r="L37" s="73">
-        <f t="shared" ref="L37" si="67">L36/$E36</f>
+      <c r="L37" s="57">
+        <f t="shared" ref="L37" si="68">L36/$E36</f>
         <v>1.4205794550127622</v>
       </c>
-      <c r="M37" s="73">
-        <f t="shared" ref="M37" si="68">M36/$E36</f>
+      <c r="M37" s="57">
+        <f t="shared" ref="M37" si="69">M36/$E36</f>
         <v>1.4463243059579656</v>
       </c>
-      <c r="N37" s="73">
-        <f t="shared" ref="N37" si="69">N36/$E36</f>
+      <c r="N37" s="57">
+        <f t="shared" ref="N37" si="70">N36/$E36</f>
         <v>1.4725357252093996</v>
       </c>
-      <c r="O37" s="73">
-        <f t="shared" ref="O37" si="70">O36/$E36</f>
+      <c r="O37" s="57">
+        <f t="shared" ref="O37" si="71">O36/$E36</f>
         <v>1.4992221682824924</v>
       </c>
-      <c r="P37" s="73">
-        <f t="shared" ref="P37" si="71">P36/$E36</f>
+      <c r="P37" s="57">
+        <f t="shared" ref="P37" si="72">P36/$E36</f>
         <v>1.5263922439301312</v>
       </c>
-      <c r="Q37" s="73">
-        <f t="shared" ref="Q37" si="72">Q36/$E36</f>
+      <c r="Q37" s="57">
+        <f t="shared" ref="Q37" si="73">Q36/$E36</f>
         <v>1.5475439465072698</v>
       </c>
-      <c r="R37" s="73">
-        <f t="shared" ref="R37" si="73">R36/$E36</f>
+      <c r="R37" s="57">
+        <f t="shared" ref="R37" si="74">R36/$E36</f>
         <v>1.5689887549513248</v>
       </c>
-      <c r="S37" s="73">
-        <f t="shared" ref="S37" si="74">S36/$E36</f>
+      <c r="S37" s="57">
+        <f t="shared" ref="S37" si="75">S36/$E36</f>
         <v>1.5907307309234751</v>
       </c>
-      <c r="T37" s="73">
-        <f t="shared" ref="T37" si="75">T36/$E36</f>
+      <c r="T37" s="57">
+        <f t="shared" ref="T37" si="76">T36/$E36</f>
         <v>1.6127739923686295</v>
       </c>
-      <c r="U37" s="73">
-        <f t="shared" ref="U37" si="76">U36/$E36</f>
+      <c r="U37" s="57">
+        <f t="shared" ref="U37" si="77">U36/$E36</f>
         <v>1.6351227142953684</v>
       </c>
-      <c r="V37" s="73">
-        <f t="shared" ref="V37" si="77">V36/$E36</f>
+      <c r="V37" s="57">
+        <f t="shared" ref="V37" si="78">V36/$E36</f>
         <v>1.6557859790084686</v>
       </c>
-      <c r="W37" s="73">
-        <f t="shared" ref="W37" si="78">W36/$E36</f>
+      <c r="W37" s="57">
+        <f t="shared" ref="W37" si="79">W36/$E36</f>
         <v>1.6767103681649338</v>
       </c>
-      <c r="X37" s="73">
-        <f t="shared" ref="X37" si="79">X36/$E36</f>
+      <c r="X37" s="57">
+        <f t="shared" ref="X37" si="80">X36/$E36</f>
         <v>1.6978991816293236</v>
       </c>
-      <c r="Y37" s="73">
-        <f t="shared" ref="Y37" si="80">Y36/$E36</f>
+      <c r="Y37" s="57">
+        <f t="shared" ref="Y37" si="81">Y36/$E36</f>
         <v>1.7193557609670291</v>
       </c>
-      <c r="Z37" s="73">
-        <f t="shared" ref="Z37" si="81">Z36/$E36</f>
+      <c r="Z37" s="57">
+        <f t="shared" ref="Z37" si="82">Z36/$E36</f>
         <v>1.7410834899712497</v>
       </c>
-      <c r="AA37" s="73">
-        <f t="shared" ref="AA37" si="82">AA36/$E36</f>
+      <c r="AA37" s="57">
+        <f t="shared" ref="AA37" si="83">AA36/$E36</f>
         <v>1.7506127508062819</v>
       </c>
-      <c r="AB37" s="73">
-        <f t="shared" ref="AB37" si="83">AB36/$E36</f>
+      <c r="AB37" s="57">
+        <f t="shared" ref="AB37" si="84">AB36/$E36</f>
         <v>1.7601941669874448</v>
       </c>
-      <c r="AC37" s="73">
-        <f t="shared" ref="AC37" si="84">AC36/$E36</f>
+      <c r="AC37" s="57">
+        <f t="shared" ref="AC37" si="85">AC36/$E36</f>
         <v>1.7698280239702611</v>
       </c>
-      <c r="AD37" s="73">
-        <f t="shared" ref="AD37" si="85">AD36/$E36</f>
+      <c r="AD37" s="57">
+        <f t="shared" ref="AD37" si="86">AD36/$E36</f>
         <v>1.7795146087726021</v>
       </c>
-      <c r="AE37" s="73">
-        <f t="shared" ref="AE37" si="86">AE36/$E36</f>
+      <c r="AE37" s="57">
+        <f t="shared" ref="AE37" si="87">AE36/$E36</f>
         <v>1.7892542099832389</v>
       </c>
-      <c r="AF37" s="73">
-        <f t="shared" ref="AF37" si="87">AF36/$E36</f>
+      <c r="AF37" s="57">
+        <f t="shared" ref="AF37" si="88">AF36/$E36</f>
         <v>1.7980644584828971</v>
       </c>
-      <c r="AG37" s="73">
-        <f t="shared" ref="AG37" si="88">AG36/$E36</f>
+      <c r="AG37" s="57">
+        <f t="shared" ref="AG37" si="89">AG36/$E36</f>
         <v>1.8069180884529983</v>
       </c>
-      <c r="AH37" s="73">
-        <f t="shared" ref="AH37" si="89">AH36/$E36</f>
+      <c r="AH37" s="57">
+        <f t="shared" ref="AH37" si="90">AH36/$E36</f>
         <v>1.815815313502952</v>
       </c>
-      <c r="AI37" s="73">
-        <f t="shared" ref="AI37" si="90">AI36/$E36</f>
+      <c r="AI37" s="57">
+        <f t="shared" ref="AI37" si="91">AI36/$E36</f>
         <v>1.8247563482939757</v>
       </c>
-      <c r="AJ37" s="73">
-        <f t="shared" ref="AJ37" si="91">AJ36/$E36</f>
+      <c r="AJ37" s="57">
+        <f t="shared" ref="AJ37" si="92">AJ36/$E36</f>
         <v>1.8337414085442729</v>
       </c>
-      <c r="AK37" s="73">
-        <f t="shared" ref="AK37" si="92">AK36/$E36</f>
+      <c r="AK37" s="57">
+        <f t="shared" ref="AK37" si="93">AK36/$E36</f>
         <v>1.8369263895829764</v>
       </c>
-      <c r="AL37" s="73">
-        <f t="shared" ref="AL37" si="93">AL36/$E36</f>
+      <c r="AL37" s="57">
+        <f t="shared" ref="AL37" si="94">AL36/$E36</f>
         <v>1.8401169025381048</v>
       </c>
-      <c r="AM37" s="73">
-        <f t="shared" ref="AM37" si="94">AM36/$E36</f>
+      <c r="AM37" s="57">
+        <f t="shared" ref="AM37" si="95">AM36/$E36</f>
         <v>1.8433129570179096</v>
       </c>
-      <c r="AN37" s="73">
-        <f t="shared" ref="AN37" si="95">AN36/$E36</f>
+      <c r="AN37" s="57">
+        <f t="shared" ref="AN37" si="96">AN36/$E36</f>
         <v>1.8465145626473309</v>
       </c>
-      <c r="AO37" s="73">
-        <f t="shared" ref="AO37" si="96">AO36/$E36</f>
+      <c r="AO37" s="57">
+        <f t="shared" ref="AO37" si="97">AO36/$E36</f>
         <v>1.8497217290680263</v>
       </c>
-      <c r="AP37" s="73">
-        <f t="shared" ref="AP37" si="97">AP36/$E36</f>
+      <c r="AP37" s="57">
+        <f t="shared" ref="AP37" si="98">AP36/$E36</f>
         <v>1.8529048947920042</v>
       </c>
-      <c r="AQ37" s="73">
-        <f t="shared" ref="AQ37" si="98">AQ36/$E36</f>
+      <c r="AQ37" s="57">
+        <f t="shared" ref="AQ37" si="99">AQ36/$E36</f>
         <v>1.8560935383907711</v>
       </c>
-      <c r="AR37" s="73">
-        <f t="shared" ref="AR37" si="99">AR36/$E36</f>
+      <c r="AR37" s="57">
+        <f t="shared" ref="AR37" si="100">AR36/$E36</f>
         <v>1.8592876692911413</v>
       </c>
-      <c r="AS37" s="73">
-        <f t="shared" ref="AS37" si="100">AS36/$E36</f>
+      <c r="AS37" s="57">
+        <f t="shared" ref="AS37" si="101">AS36/$E36</f>
         <v>1.8624872969361514</v>
       </c>
-      <c r="AT37" s="73">
-        <f t="shared" ref="AT37" si="101">AT36/$E36</f>
+      <c r="AT37" s="57">
+        <f t="shared" ref="AT37" si="102">AT36/$E36</f>
         <v>1.8656924307850895</v>
       </c>
     </row>
@@ -17862,340 +17861,340 @@
         <v>6003.4063882649998</v>
       </c>
       <c r="F38">
-        <f t="shared" ref="F38:AT38" si="102">F44+F45</f>
+        <f t="shared" ref="F38:AT38" si="103">F44+F45</f>
         <v>6075.4650161250001</v>
       </c>
       <c r="G38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>6987.7955309999998</v>
       </c>
       <c r="H38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>7760.2091208017628</v>
       </c>
       <c r="I38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>8211</v>
       </c>
       <c r="J38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>8544.4555111879326</v>
       </c>
       <c r="K38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>8943.7019173411754</v>
       </c>
       <c r="L38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>9350.4103583711767</v>
       </c>
       <c r="M38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>9699.6830655745616</v>
       </c>
       <c r="N38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>10010.375815500898</v>
       </c>
       <c r="O38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>10294.550732344846</v>
       </c>
       <c r="P38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>10577.516277278155</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>10851.072101638852</v>
       </c>
       <c r="R38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>11140.646986368889</v>
       </c>
       <c r="S38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>11435.168318011227</v>
       </c>
       <c r="T38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>11733.428846177005</v>
       </c>
       <c r="U38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>12029.77141787775</v>
       </c>
       <c r="V38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>12344.311592869972</v>
       </c>
       <c r="W38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>12654.493271975423</v>
       </c>
       <c r="X38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>12963.247717721864</v>
       </c>
       <c r="Y38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>13269.397348221606</v>
       </c>
       <c r="Z38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>13571.488761336941</v>
       </c>
       <c r="AA38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>13877.185006821681</v>
       </c>
       <c r="AB38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>14175.947402720092</v>
       </c>
       <c r="AC38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>14465.872164011329</v>
       </c>
       <c r="AD38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>14745.094069266042</v>
       </c>
       <c r="AE38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>15011.528088885952</v>
       </c>
       <c r="AF38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>15279.949050443629</v>
       </c>
       <c r="AG38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>15532.312779479405</v>
       </c>
       <c r="AH38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>15766.558947430789</v>
       </c>
       <c r="AI38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>15980.954161897744</v>
       </c>
       <c r="AJ38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16173.674033819889</v>
       </c>
       <c r="AK38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16366.022414249017</v>
       </c>
       <c r="AL38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16531.754833050923</v>
       </c>
       <c r="AM38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16668.417993684769</v>
       </c>
       <c r="AN38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16773.623084200302</v>
       </c>
       <c r="AO38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16845.078331063185</v>
       </c>
       <c r="AP38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16897.924794373586</v>
       </c>
       <c r="AQ38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16913.175165262932</v>
       </c>
       <c r="AR38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16888.958007351808</v>
       </c>
       <c r="AS38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16823.651497812793</v>
       </c>
       <c r="AT38">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>16692.694553475696</v>
       </c>
     </row>
     <row r="39" spans="3:46">
-      <c r="D39" s="73" t="s">
+      <c r="D39" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E39" s="73">
+      <c r="E39" s="57">
         <f>E38/$E$38</f>
         <v>1</v>
       </c>
-      <c r="F39" s="73">
-        <f t="shared" ref="F39:AT39" si="103">F38/$E$38</f>
+      <c r="F39" s="57">
+        <f t="shared" ref="F39:AT39" si="104">F38/$E$38</f>
         <v>1.0120029568547708</v>
       </c>
-      <c r="G39" s="73">
-        <f t="shared" si="103"/>
+      <c r="G39" s="57">
+        <f t="shared" si="104"/>
         <v>1.1639717652063684</v>
       </c>
-      <c r="H39" s="73">
-        <f t="shared" si="103"/>
+      <c r="H39" s="57">
+        <f t="shared" si="104"/>
         <v>1.2926343177384805</v>
       </c>
-      <c r="I39" s="73">
-        <f t="shared" si="103"/>
+      <c r="I39" s="57">
+        <f t="shared" si="104"/>
         <v>1.3677235004530488</v>
       </c>
-      <c r="J39" s="73">
-        <f t="shared" si="103"/>
+      <c r="J39" s="57">
+        <f t="shared" si="104"/>
         <v>1.423267884694593</v>
       </c>
-      <c r="K39" s="73">
-        <f t="shared" si="103"/>
+      <c r="K39" s="57">
+        <f t="shared" si="104"/>
         <v>1.4897711963700544</v>
       </c>
-      <c r="L39" s="73">
-        <f t="shared" si="103"/>
+      <c r="L39" s="57">
+        <f t="shared" si="104"/>
         <v>1.5575174748537171</v>
       </c>
-      <c r="M39" s="73">
-        <f t="shared" si="103"/>
+      <c r="M39" s="57">
+        <f t="shared" si="104"/>
         <v>1.6156965626273045</v>
       </c>
-      <c r="N39" s="73">
-        <f t="shared" si="103"/>
+      <c r="N39" s="57">
+        <f t="shared" si="104"/>
         <v>1.6674493059587663</v>
       </c>
-      <c r="O39" s="73">
-        <f t="shared" si="103"/>
+      <c r="O39" s="57">
+        <f t="shared" si="104"/>
         <v>1.7147849181870891</v>
       </c>
-      <c r="P39" s="73">
-        <f t="shared" si="103"/>
+      <c r="P39" s="57">
+        <f t="shared" si="104"/>
         <v>1.7619190827984386</v>
       </c>
-      <c r="Q39" s="73">
-        <f t="shared" si="103"/>
+      <c r="Q39" s="57">
+        <f t="shared" si="104"/>
         <v>1.8074858505080882</v>
       </c>
-      <c r="R39" s="73">
-        <f t="shared" si="103"/>
+      <c r="R39" s="57">
+        <f t="shared" si="104"/>
         <v>1.855720946718812</v>
       </c>
-      <c r="S39" s="73">
-        <f t="shared" si="103"/>
+      <c r="S39" s="57">
+        <f t="shared" si="104"/>
         <v>1.9047799829716376</v>
       </c>
-      <c r="T39" s="73">
-        <f t="shared" si="103"/>
+      <c r="T39" s="57">
+        <f t="shared" si="104"/>
         <v>1.9544618650359262</v>
       </c>
-      <c r="U39" s="73">
-        <f t="shared" si="103"/>
+      <c r="U39" s="57">
+        <f t="shared" si="104"/>
         <v>2.0038242690670796</v>
       </c>
-      <c r="V39" s="73">
-        <f t="shared" si="103"/>
+      <c r="V39" s="57">
+        <f t="shared" si="104"/>
         <v>2.0562178860654328</v>
       </c>
-      <c r="W39" s="73">
-        <f t="shared" si="103"/>
+      <c r="W39" s="57">
+        <f t="shared" si="104"/>
         <v>2.1078854992577982</v>
       </c>
-      <c r="X39" s="73">
-        <f t="shared" si="103"/>
+      <c r="X39" s="57">
+        <f t="shared" si="104"/>
         <v>2.1593153751945615</v>
       </c>
-      <c r="Y39" s="73">
-        <f t="shared" si="103"/>
+      <c r="Y39" s="57">
+        <f t="shared" si="104"/>
         <v>2.2103113615895817</v>
       </c>
-      <c r="Z39" s="73">
-        <f t="shared" si="103"/>
+      <c r="Z39" s="57">
+        <f t="shared" si="104"/>
         <v>2.2606313621988758</v>
       </c>
-      <c r="AA39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AA39" s="57">
+        <f t="shared" si="104"/>
         <v>2.3115518273005375</v>
       </c>
-      <c r="AB39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AB39" s="57">
+        <f t="shared" si="104"/>
         <v>2.3613173065262001</v>
       </c>
-      <c r="AC39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AC39" s="57">
+        <f t="shared" si="104"/>
         <v>2.4096106824099248</v>
       </c>
-      <c r="AD39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AD39" s="57">
+        <f t="shared" si="104"/>
         <v>2.4561212611041334</v>
       </c>
-      <c r="AE39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AE39" s="57">
+        <f t="shared" si="104"/>
         <v>2.5005017348532896</v>
       </c>
-      <c r="AF39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AF39" s="57">
+        <f t="shared" si="104"/>
         <v>2.5452131776905369</v>
       </c>
-      <c r="AG39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AG39" s="57">
+        <f t="shared" si="104"/>
         <v>2.587249933611155</v>
       </c>
-      <c r="AH39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AH39" s="57">
+        <f t="shared" si="104"/>
         <v>2.6262688093629731</v>
       </c>
-      <c r="AI39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AI39" s="57">
+        <f t="shared" si="104"/>
         <v>2.6619810701364632</v>
       </c>
-      <c r="AJ39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AJ39" s="57">
+        <f t="shared" si="104"/>
         <v>2.6940828236174301</v>
       </c>
-      <c r="AK39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AK39" s="57">
+        <f t="shared" si="104"/>
         <v>2.7261226969808452</v>
       </c>
-      <c r="AL39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AL39" s="57">
+        <f t="shared" si="104"/>
         <v>2.7537290937634897</v>
       </c>
-      <c r="AM39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AM39" s="57">
+        <f t="shared" si="104"/>
         <v>2.776493363212412</v>
       </c>
-      <c r="AN39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AN39" s="57">
+        <f t="shared" si="104"/>
         <v>2.7940175959082327</v>
       </c>
-      <c r="AO39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AO39" s="57">
+        <f t="shared" si="104"/>
         <v>2.8059200463241432</v>
       </c>
-      <c r="AP39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AP39" s="57">
+        <f t="shared" si="104"/>
         <v>2.8147227926139333</v>
       </c>
-      <c r="AQ39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AQ39" s="57">
+        <f t="shared" si="104"/>
         <v>2.8172630788952611</v>
       </c>
-      <c r="AR39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AR39" s="57">
+        <f t="shared" si="104"/>
         <v>2.8132291760832739</v>
       </c>
-      <c r="AS39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AS39" s="57">
+        <f t="shared" si="104"/>
         <v>2.8023509337462782</v>
       </c>
-      <c r="AT39" s="73">
-        <f t="shared" si="103"/>
+      <c r="AT39" s="57">
+        <f t="shared" si="104"/>
         <v>2.7805371607201703</v>
       </c>
     </row>
@@ -18211,31 +18210,31 @@
         <v>61859.382378924005</v>
       </c>
       <c r="F40">
-        <f t="shared" ref="F40:AT40" si="104">F46+F47</f>
+        <f t="shared" ref="F40:AT40" si="105">F46+F47</f>
         <v>62040.737315400009</v>
       </c>
       <c r="G40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>71251.68733320001</v>
       </c>
       <c r="H40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>68856.53778684001</v>
       </c>
       <c r="I40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>73950.664132289763</v>
       </c>
       <c r="J40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>74379.692378560794</v>
       </c>
       <c r="K40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>74876.185184986811</v>
       </c>
       <c r="L40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>75362.605315013308</v>
       </c>
       <c r="M40">
@@ -18243,308 +18242,308 @@
         <v>75764.758806089143</v>
       </c>
       <c r="N40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>76111.449975596304</v>
       </c>
       <c r="O40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>76420.114924364432</v>
       </c>
       <c r="P40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>76720.194063674731</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>77003.64240261291</v>
       </c>
       <c r="R40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>77297.205506841128</v>
       </c>
       <c r="S40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>77589.131049226096</v>
       </c>
       <c r="T40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>77878.236359679591</v>
       </c>
       <c r="U40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>78159.223968975843</v>
       </c>
       <c r="V40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>78451.168905660481</v>
       </c>
       <c r="W40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>78732.780574274802</v>
       </c>
       <c r="X40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>79007.20705105293</v>
       </c>
       <c r="Y40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>79273.763128579594</v>
       </c>
       <c r="Z40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>79531.584323124669</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>79787.504311529177</v>
       </c>
       <c r="AB40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>80032.896874308077</v>
       </c>
       <c r="AC40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>80266.728749249363</v>
       </c>
       <c r="AD40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>80488.059821008399</v>
       </c>
       <c r="AE40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>80695.826332643497</v>
       </c>
       <c r="AF40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>80901.957924783346</v>
       </c>
       <c r="AG40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81092.840384261945</v>
       </c>
       <c r="AH40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81267.551621759427</v>
       </c>
       <c r="AI40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81425.420783927708</v>
       </c>
       <c r="AJ40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81565.69755611998</v>
       </c>
       <c r="AK40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81704.273984091618</v>
       </c>
       <c r="AL40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81822.472238386777</v>
       </c>
       <c r="AM40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81919.101144218512</v>
       </c>
       <c r="AN40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81992.964580826534</v>
       </c>
       <c r="AO40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>82042.862885833936</v>
       </c>
       <c r="AP40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>82079.632211043747</v>
       </c>
       <c r="AQ40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>82090.214616439785</v>
       </c>
       <c r="AR40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>82073.423043590316</v>
       </c>
       <c r="AS40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>82028.085485654839</v>
       </c>
       <c r="AT40">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>81936.86911152293</v>
       </c>
     </row>
     <row r="41" spans="3:46">
-      <c r="D41" s="73" t="s">
+      <c r="D41" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="73">
+      <c r="E41" s="57">
         <f>E40/$E40</f>
         <v>1</v>
       </c>
-      <c r="F41" s="73">
-        <f t="shared" ref="F41" si="105">F40/$E40</f>
+      <c r="F41" s="57">
+        <f t="shared" ref="F41" si="106">F40/$E40</f>
         <v>1.0029317288582855</v>
       </c>
-      <c r="G41" s="73">
-        <f t="shared" ref="G41" si="106">G40/$E40</f>
+      <c r="G41" s="57">
+        <f t="shared" ref="G41" si="107">G40/$E40</f>
         <v>1.1518331511417748</v>
       </c>
-      <c r="H41" s="73">
-        <f t="shared" ref="H41" si="107">H40/$E40</f>
+      <c r="H41" s="57">
+        <f t="shared" ref="H41" si="108">H40/$E40</f>
         <v>1.1131138905502553</v>
       </c>
-      <c r="I41" s="73">
-        <f t="shared" ref="I41" si="108">I40/$E40</f>
+      <c r="I41" s="57">
+        <f t="shared" ref="I41" si="109">I40/$E40</f>
         <v>1.195463990883384</v>
       </c>
-      <c r="J41" s="73">
-        <f t="shared" ref="J41" si="109">J40/$E40</f>
+      <c r="J41" s="57">
+        <f t="shared" ref="J41" si="110">J40/$E40</f>
         <v>1.2023995312941009</v>
       </c>
-      <c r="K41" s="73">
-        <f t="shared" ref="K41" si="110">K40/$E40</f>
+      <c r="K41" s="57">
+        <f t="shared" ref="K41" si="111">K40/$E40</f>
         <v>1.2104256833074645</v>
       </c>
-      <c r="L41" s="73">
-        <f t="shared" ref="L41" si="111">L40/$E40</f>
+      <c r="L41" s="57">
+        <f t="shared" ref="L41" si="112">L40/$E40</f>
         <v>1.2182890034914082</v>
       </c>
-      <c r="M41" s="73">
-        <f t="shared" ref="M41" si="112">M40/$E40</f>
+      <c r="M41" s="57">
+        <f t="shared" ref="M41" si="113">M40/$E40</f>
         <v>1.2247900947666559</v>
       </c>
-      <c r="N41" s="73">
-        <f t="shared" ref="N41" si="113">N40/$E40</f>
+      <c r="N41" s="57">
+        <f t="shared" ref="N41" si="114">N40/$E40</f>
         <v>1.2303945989853287</v>
       </c>
-      <c r="O41" s="73">
-        <f t="shared" ref="O41" si="114">O40/$E40</f>
+      <c r="O41" s="57">
+        <f t="shared" ref="O41" si="115">O40/$E40</f>
         <v>1.235384382861239</v>
       </c>
-      <c r="P41" s="73">
-        <f t="shared" ref="P41" si="115">P40/$E40</f>
+      <c r="P41" s="57">
+        <f t="shared" ref="P41" si="116">P40/$E40</f>
         <v>1.2402353711474159</v>
       </c>
-      <c r="Q41" s="73">
-        <f t="shared" ref="Q41" si="116">Q40/$E40</f>
+      <c r="Q41" s="57">
+        <f t="shared" ref="Q41" si="117">Q40/$E40</f>
         <v>1.2448175109625517</v>
       </c>
-      <c r="R41" s="73">
-        <f t="shared" ref="R41" si="117">R40/$E40</f>
+      <c r="R41" s="57">
+        <f t="shared" ref="R41" si="118">R40/$E40</f>
         <v>1.2495631630033364</v>
       </c>
-      <c r="S41" s="73">
-        <f t="shared" ref="S41" si="118">S40/$E40</f>
+      <c r="S41" s="57">
+        <f t="shared" ref="S41" si="119">S40/$E40</f>
         <v>1.2542823427163952</v>
       </c>
-      <c r="T41" s="73">
-        <f t="shared" ref="T41" si="119">T40/$E40</f>
+      <c r="T41" s="57">
+        <f t="shared" ref="T41" si="120">T40/$E40</f>
         <v>1.2589559314160457</v>
       </c>
-      <c r="U41" s="73">
-        <f t="shared" ref="U41" si="120">U40/$E40</f>
+      <c r="U41" s="57">
+        <f t="shared" ref="U41" si="121">U40/$E40</f>
         <v>1.2634982918226698</v>
       </c>
-      <c r="V41" s="73">
-        <f t="shared" ref="V41" si="121">V40/$E40</f>
+      <c r="V41" s="57">
+        <f t="shared" ref="V41" si="122">V40/$E40</f>
         <v>1.2682177850580907</v>
       </c>
-      <c r="W41" s="73">
-        <f t="shared" ref="W41" si="122">W40/$E40</f>
+      <c r="W41" s="57">
+        <f t="shared" ref="W41" si="123">W40/$E40</f>
         <v>1.2727702338182365</v>
       </c>
-      <c r="X41" s="73">
-        <f t="shared" ref="X41" si="123">X40/$E40</f>
+      <c r="X41" s="57">
+        <f t="shared" ref="X41" si="124">X40/$E40</f>
         <v>1.2772065289480052</v>
       </c>
-      <c r="Y41" s="73">
-        <f t="shared" ref="Y41" si="124">Y40/$E40</f>
+      <c r="Y41" s="57">
+        <f t="shared" ref="Y41" si="125">Y40/$E40</f>
         <v>1.2815155935922957</v>
       </c>
-      <c r="Z41" s="73">
-        <f t="shared" ref="Z41" si="125">Z40/$E40</f>
+      <c r="Z41" s="57">
+        <f t="shared" ref="Z41" si="126">Z40/$E40</f>
         <v>1.2856834527695145</v>
       </c>
-      <c r="AA41" s="73">
-        <f t="shared" ref="AA41" si="126">AA40/$E40</f>
+      <c r="AA41" s="57">
+        <f t="shared" ref="AA41" si="127">AA40/$E40</f>
         <v>1.289820577625318</v>
       </c>
-      <c r="AB41" s="73">
-        <f t="shared" ref="AB41" si="127">AB40/$E40</f>
+      <c r="AB41" s="57">
+        <f t="shared" ref="AB41" si="128">AB40/$E40</f>
         <v>1.2937875193137385</v>
       </c>
-      <c r="AC41" s="73">
-        <f t="shared" ref="AC41" si="128">AC40/$E40</f>
+      <c r="AC41" s="57">
+        <f t="shared" ref="AC41" si="129">AC40/$E40</f>
         <v>1.2975675744314721</v>
       </c>
-      <c r="AD41" s="73">
-        <f t="shared" ref="AD41" si="129">AD40/$E40</f>
+      <c r="AD41" s="57">
+        <f t="shared" ref="AD41" si="130">AD40/$E40</f>
         <v>1.3011455453592007</v>
       </c>
-      <c r="AE41" s="73">
-        <f t="shared" ref="AE41" si="130">AE40/$E40</f>
+      <c r="AE41" s="57">
+        <f t="shared" ref="AE41" si="131">AE40/$E40</f>
         <v>1.304504235725076</v>
       </c>
-      <c r="AF41" s="73">
-        <f t="shared" ref="AF41" si="131">AF40/$E40</f>
+      <c r="AF41" s="57">
+        <f t="shared" ref="AF41" si="132">AF40/$E40</f>
         <v>1.3078364964786215</v>
       </c>
-      <c r="AG41" s="73">
-        <f t="shared" ref="AG41" si="132">AG40/$E40</f>
+      <c r="AG41" s="57">
+        <f t="shared" ref="AG41" si="133">AG40/$E40</f>
         <v>1.3109222443819766</v>
       </c>
-      <c r="AH41" s="73">
-        <f t="shared" ref="AH41" si="133">AH40/$E40</f>
+      <c r="AH41" s="57">
+        <f t="shared" ref="AH41" si="134">AH40/$E40</f>
         <v>1.3137465732190683</v>
       </c>
-      <c r="AI41" s="73">
-        <f t="shared" ref="AI41" si="134">AI40/$E40</f>
+      <c r="AI41" s="57">
+        <f t="shared" ref="AI41" si="135">AI40/$E40</f>
         <v>1.3162986381782888</v>
       </c>
-      <c r="AJ41" s="73">
-        <f t="shared" ref="AJ41" si="135">AJ40/$E40</f>
+      <c r="AJ41" s="57">
+        <f t="shared" ref="AJ41" si="136">AJ40/$E40</f>
         <v>1.3185663099007932</v>
       </c>
-      <c r="AK41" s="73">
-        <f t="shared" ref="AK41" si="136">AK40/$E40</f>
+      <c r="AK41" s="57">
+        <f t="shared" ref="AK41" si="137">AK40/$E40</f>
         <v>1.3208064943747149</v>
       </c>
-      <c r="AL41" s="73">
-        <f t="shared" ref="AL41" si="137">AL40/$E40</f>
+      <c r="AL41" s="57">
+        <f t="shared" ref="AL41" si="138">AL40/$E40</f>
         <v>1.3227172514781582</v>
       </c>
-      <c r="AM41" s="73">
-        <f t="shared" ref="AM41" si="138">AM40/$E40</f>
+      <c r="AM41" s="57">
+        <f t="shared" ref="AM41" si="139">AM40/$E40</f>
         <v>1.3242793250410632</v>
       </c>
-      <c r="AN41" s="73">
-        <f t="shared" ref="AN41" si="139">AN40/$E40</f>
+      <c r="AN41" s="57">
+        <f t="shared" ref="AN41" si="140">AN40/$E40</f>
         <v>1.3254733789382644</v>
       </c>
-      <c r="AO41" s="73">
-        <f t="shared" ref="AO41" si="140">AO40/$E40</f>
+      <c r="AO41" s="57">
+        <f t="shared" ref="AO41" si="141">AO40/$E40</f>
         <v>1.3262800197918982</v>
       </c>
-      <c r="AP41" s="73">
-        <f t="shared" ref="AP41" si="141">AP40/$E40</f>
+      <c r="AP41" s="57">
+        <f t="shared" ref="AP41" si="142">AP40/$E40</f>
         <v>1.3268744215430277</v>
       </c>
-      <c r="AQ41" s="73">
-        <f t="shared" ref="AQ41" si="142">AQ40/$E40</f>
+      <c r="AQ41" s="57">
+        <f t="shared" ref="AQ41" si="143">AQ40/$E40</f>
         <v>1.3270454934966922</v>
       </c>
-      <c r="AR41" s="73">
-        <f t="shared" ref="AR41" si="143">AR40/$E40</f>
+      <c r="AR41" s="57">
+        <f t="shared" ref="AR41" si="144">AR40/$E40</f>
         <v>1.3267740460265798</v>
       </c>
-      <c r="AS41" s="73">
-        <f t="shared" ref="AS41" si="144">AS40/$E40</f>
+      <c r="AS41" s="57">
+        <f t="shared" ref="AS41" si="145">AS40/$E40</f>
         <v>1.3260411328258344</v>
       </c>
-      <c r="AT41" s="73">
-        <f t="shared" ref="AT41" si="145">AT40/$E40</f>
+      <c r="AT41" s="57">
+        <f t="shared" ref="AT41" si="146">AT40/$E40</f>
         <v>1.3245665566075793</v>
       </c>
     </row>
@@ -19383,8 +19382,8 @@
         <v>0.93176953330484824</v>
       </c>
       <c r="D2">
-        <f>passenger!G36</f>
-        <v>0.98544581794857811</v>
+        <f>passenger!G36*0.975</f>
+        <v>0.9608096724998636</v>
       </c>
       <c r="E2">
         <f>passenger!H36</f>
@@ -19749,144 +19748,144 @@
         <v>1.2495194484549734</v>
       </c>
       <c r="I4">
-        <f>passenger!L30</f>
-        <v>1.3240994256313294</v>
+        <f>passenger!L30*1.02</f>
+        <v>1.350581414143956</v>
       </c>
       <c r="J4">
-        <f>passenger!M30</f>
-        <v>1.4031308525250177</v>
+        <f>passenger!M30*1.04</f>
+        <v>1.4592560866260185</v>
       </c>
       <c r="K4">
-        <f>passenger!N30</f>
-        <v>1.4868794224941768</v>
+        <f>passenger!N30*1.06</f>
+        <v>1.5760921878438274</v>
       </c>
       <c r="L4">
-        <f>passenger!O30</f>
-        <v>1.575626687317246</v>
+        <f>passenger!O30*1.08</f>
+        <v>1.7016768223026257</v>
       </c>
       <c r="M4">
-        <f>passenger!P30</f>
-        <v>1.6696710037333518</v>
+        <f>passenger!P30*1.1</f>
+        <v>1.836638104106687</v>
       </c>
       <c r="N4">
-        <f>passenger!Q30</f>
-        <v>1.741146149806418</v>
+        <f>passenger!Q30*1.15</f>
+        <v>2.0023180722773808</v>
       </c>
       <c r="O4">
-        <f>passenger!R30</f>
-        <v>1.8156809983566449</v>
+        <f>passenger!R30*1.14</f>
+        <v>2.069876338126575</v>
       </c>
       <c r="P4">
-        <f>passenger!S30</f>
-        <v>1.8934065288889803</v>
+        <f>passenger!S30*1.1</f>
+        <v>2.0827471817778784</v>
       </c>
       <c r="Q4">
-        <f>passenger!T30</f>
-        <v>1.9744593278688025</v>
+        <f>passenger!T30*1.06</f>
+        <v>2.0929268875409308</v>
       </c>
       <c r="R4">
-        <f>passenger!U30</f>
-        <v>2.0589818287442441</v>
+        <f>passenger!U30*1.02</f>
+        <v>2.100161465319129</v>
       </c>
       <c r="S4">
-        <f>passenger!V30</f>
-        <v>2.065687093140415</v>
+        <f>passenger!V30*1.02</f>
+        <v>2.1070008350032232</v>
       </c>
       <c r="T4">
-        <f>passenger!W30</f>
-        <v>2.0724141938490757</v>
+        <f>passenger!W30*1.015</f>
+        <v>2.1035004067568117</v>
       </c>
       <c r="U4">
-        <f>passenger!X30</f>
-        <v>2.0791632019821926</v>
+        <f>passenger!X30*1.01</f>
+        <v>2.0999548340020144</v>
       </c>
       <c r="V4">
-        <f>passenger!Y30</f>
-        <v>2.0859341888833169</v>
+        <f>passenger!Y30*1.01</f>
+        <v>2.1067935307721499</v>
       </c>
       <c r="W4">
-        <f>passenger!Z30</f>
-        <v>2.0927272261283352</v>
+        <f>passenger!Z30*1.01</f>
+        <v>2.1136544983896184</v>
       </c>
       <c r="X4">
-        <f>passenger!AA30</f>
-        <v>2.1036838040682193</v>
+        <f>passenger!AA30*1.01</f>
+        <v>2.1247206421089015</v>
       </c>
       <c r="Y4">
-        <f>passenger!AB30</f>
-        <v>2.1146977457192713</v>
+        <f>passenger!AB30*1.01</f>
+        <v>2.1358447231764641</v>
       </c>
       <c r="Z4">
-        <f>passenger!AC30</f>
-        <v>2.125769351412067</v>
+        <f>passenger!AC30*1.01</f>
+        <v>2.1470270449261877</v>
       </c>
       <c r="AA4">
-        <f>passenger!AD30</f>
-        <v>2.1368989230495776</v>
+        <f>passenger!AD30*1.01</f>
+        <v>2.1582679122800736</v>
       </c>
       <c r="AB4">
-        <f>passenger!AE30</f>
-        <v>2.1480867641154009</v>
+        <f>passenger!AE30*1.01</f>
+        <v>2.1695676317565549</v>
       </c>
       <c r="AC4">
-        <f>passenger!AF30</f>
-        <v>2.1340474751584533</v>
+        <f>passenger!AF30*1.01</f>
+        <v>2.1553879499100379</v>
       </c>
       <c r="AD4">
-        <f>passenger!AG30</f>
-        <v>2.1200999430326122</v>
+        <f>passenger!AG30*1.01</f>
+        <v>2.1413009424629381</v>
       </c>
       <c r="AE4">
-        <f>passenger!AH30</f>
-        <v>2.1062435680411209</v>
+        <f>passenger!AH30*1.01</f>
+        <v>2.1273060037215323</v>
       </c>
       <c r="AF4">
-        <f>passenger!AI30</f>
-        <v>2.0924777544066706</v>
+        <f>passenger!AI30*1.01</f>
+        <v>2.1134025319507375</v>
       </c>
       <c r="AG4">
-        <f>passenger!AJ30</f>
-        <v>2.0788019102457862</v>
+        <f>passenger!AJ30*1.01</f>
+        <v>2.0995899293482441</v>
       </c>
       <c r="AH4">
-        <f>passenger!AK30</f>
-        <v>2.0319917609957465</v>
+        <f>passenger!AK30*1.01</f>
+        <v>2.0523116786057041</v>
       </c>
       <c r="AI4">
-        <f>passenger!AL30</f>
-        <v>1.9862356756572381</v>
+        <f>passenger!AL30*1.01</f>
+        <v>2.0060980324138105</v>
       </c>
       <c r="AJ4">
-        <f>passenger!AM30</f>
-        <v>1.9415099189773843</v>
+        <f>passenger!AM30*1.01</f>
+        <v>1.9609250181671583</v>
       </c>
       <c r="AK4">
-        <f>passenger!AN30</f>
-        <v>1.8977912901701703</v>
+        <f>passenger!AN30*1.01</f>
+        <v>1.9167692030718722</v>
       </c>
       <c r="AL4">
-        <f>passenger!AO30</f>
-        <v>1.8550571108813958</v>
+        <f>passenger!AO30*1.01</f>
+        <v>1.8736076819902099</v>
       </c>
       <c r="AM4">
-        <f>passenger!AP30</f>
-        <v>1.7962182767856762</v>
+        <f>passenger!AP30*1.01</f>
+        <v>1.8141804595535331</v>
       </c>
       <c r="AN4">
-        <f>passenger!AQ30</f>
-        <v>1.7392456970372951</v>
+        <f>passenger!AQ30*1.01</f>
+        <v>1.7566381540076681</v>
       </c>
       <c r="AO4">
-        <f>passenger!AR30</f>
-        <v>1.6840801776474104</v>
+        <f>passenger!AR30*1.01</f>
+        <v>1.7009209794238844</v>
       </c>
       <c r="AP4">
-        <f>passenger!AS30</f>
-        <v>1.6306644021463503</v>
+        <f>passenger!AS30*1.01</f>
+        <v>1.6469710461678138</v>
       </c>
       <c r="AQ4">
-        <f>passenger!AT30</f>
-        <v>1.5789428720323273</v>
+        <f>passenger!AT30*1.01</f>
+        <v>1.5947323007526506</v>
       </c>
     </row>
     <row r="5" spans="1:43">
@@ -20380,7 +20379,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -20701,8 +20700,8 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <f>freight!AM22</f>
-        <v>1.0575955367833962</v>
+        <f>freight!AM22*0.95</f>
+        <v>1.0047157599442265</v>
       </c>
       <c r="E3">
         <f>freight!AN22</f>
@@ -20894,48 +20893,48 @@
         <v>1.3984176791404332</v>
       </c>
       <c r="I4">
-        <f>freight!L32</f>
-        <v>1.4529251443088298</v>
+        <f>freight!L32*1.02</f>
+        <v>1.4819836471950065</v>
       </c>
       <c r="J4">
-        <f>freight!M32</f>
-        <v>1.4994441506473171</v>
+        <f>freight!M32*1.04</f>
+        <v>1.5594219166732097</v>
       </c>
       <c r="K4">
-        <f>freight!N32</f>
-        <v>1.5406118957354304</v>
+        <f>freight!N32*1.06</f>
+        <v>1.6330486094795564</v>
       </c>
       <c r="L4">
-        <f>freight!O32</f>
-        <v>1.5780989933025782</v>
+        <f>freight!O32*1.08</f>
+        <v>1.7043469127667845</v>
       </c>
       <c r="M4">
-        <f>freight!P32</f>
-        <v>1.6152793551582547</v>
+        <f>freight!P32*1.1</f>
+        <v>1.7768072906740804</v>
       </c>
       <c r="N4">
-        <f>freight!Q32</f>
-        <v>1.6510859577662245</v>
+        <f>freight!Q32*1.12</f>
+        <v>1.8492162726981716</v>
       </c>
       <c r="O4">
-        <f>freight!R32</f>
-        <v>1.6888528402657748</v>
+        <f>freight!R32*1.1</f>
+        <v>1.8577381242923523</v>
       </c>
       <c r="P4">
-        <f>freight!S32</f>
-        <v>1.7271222145467906</v>
+        <f>freight!S32*1.08</f>
+        <v>1.8652919917105339</v>
       </c>
       <c r="Q4">
-        <f>freight!T32</f>
-        <v>1.7657348550500753</v>
+        <f>freight!T32*1.06</f>
+        <v>1.8716789463530799</v>
       </c>
       <c r="R4">
-        <f>freight!U32</f>
-        <v>1.8039598821254301</v>
+        <f>freight!U32*1.04</f>
+        <v>1.8761182774104475</v>
       </c>
       <c r="S4">
-        <f>freight!V32</f>
-        <v>1.8443894253187751</v>
+        <f>freight!V32*1.02</f>
+        <v>1.8812772138251508</v>
       </c>
       <c r="T4">
         <f>freight!W32</f>
@@ -21240,76 +21239,76 @@
         <v>1.3952928673681615</v>
       </c>
       <c r="I6">
-        <f>freight!L37</f>
-        <v>1.4205794550127622</v>
+        <f>freight!L37*1.02</f>
+        <v>1.4489910441130174</v>
       </c>
       <c r="J6">
-        <f>freight!M37</f>
-        <v>1.4463243059579656</v>
+        <f>freight!M37*1.04</f>
+        <v>1.5041772781962843</v>
       </c>
       <c r="K6">
-        <f>freight!N37</f>
-        <v>1.4725357252093996</v>
+        <f>freight!N37*1.06</f>
+        <v>1.5608878687219636</v>
       </c>
       <c r="L6">
-        <f>freight!O37</f>
-        <v>1.4992221682824924</v>
+        <f>freight!O37*1.08</f>
+        <v>1.6191599417450919</v>
       </c>
       <c r="M6">
-        <f>freight!P37</f>
-        <v>1.5263922439301312</v>
+        <f>freight!P37*1.1</f>
+        <v>1.6790314683231444</v>
       </c>
       <c r="N6">
-        <f>freight!Q37</f>
-        <v>1.5475439465072698</v>
+        <f>freight!Q37*1.12</f>
+        <v>1.7332492200881424</v>
       </c>
       <c r="O6">
-        <f>freight!R37</f>
-        <v>1.5689887549513248</v>
+        <f>freight!R37*1.11</f>
+        <v>1.7415775179959707</v>
       </c>
       <c r="P6">
-        <f>freight!S37</f>
-        <v>1.5907307309234751</v>
+        <f>freight!S37*1.1</f>
+        <v>1.7498038040158228</v>
       </c>
       <c r="Q6">
-        <f>freight!T37</f>
-        <v>1.6127739923686295</v>
+        <f>freight!T37*1.08</f>
+        <v>1.7417959117581199</v>
       </c>
       <c r="R6">
-        <f>freight!U37</f>
-        <v>1.6351227142953684</v>
+        <f>freight!U37*1.07</f>
+        <v>1.7495813042960442</v>
       </c>
       <c r="S6">
-        <f>freight!V37</f>
-        <v>1.6557859790084686</v>
+        <f>freight!V37*1.06</f>
+        <v>1.7551331377489767</v>
       </c>
       <c r="T6">
-        <f>freight!W37</f>
-        <v>1.6767103681649338</v>
+        <f>freight!W37*1.05</f>
+        <v>1.7605458865731805</v>
       </c>
       <c r="U6">
-        <f>freight!X37</f>
-        <v>1.6978991816293236</v>
+        <f>freight!X37*1.04</f>
+        <v>1.7658151488944966</v>
       </c>
       <c r="V6">
-        <f>freight!Y37</f>
-        <v>1.7193557609670291</v>
+        <f>freight!Y37*1.03</f>
+        <v>1.77093643379604</v>
       </c>
       <c r="W6">
-        <f>freight!Z37</f>
-        <v>1.7410834899712497</v>
+        <f>freight!Z37*1.02</f>
+        <v>1.7759051597706748</v>
       </c>
       <c r="X6">
-        <f>freight!AA37</f>
-        <v>1.7506127508062819</v>
+        <f>freight!AA37*1.015</f>
+        <v>1.7768719420683758</v>
       </c>
       <c r="Y6">
-        <f>freight!AB37</f>
-        <v>1.7601941669874448</v>
+        <f>freight!AB37*1.01</f>
+        <v>1.7777961086573193</v>
       </c>
       <c r="Z6">
-        <f>freight!AC37</f>
-        <v>1.7698280239702611</v>
+        <f>freight!AC37*1.005</f>
+        <v>1.7786771640901122</v>
       </c>
       <c r="AA6">
         <f>freight!AD37</f>
@@ -21550,6 +21549,11 @@
       <c r="AQ7" cm="1">
         <f t="array" ref="AQ7">TREND(R7:AP7,$R$1:$AP$1,$AQ$1,TRUE)</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="14:14">
+      <c r="N24" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -21560,6 +21564,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -21793,15 +21806,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -21812,6 +21816,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0447F67E-7323-42C4-9E2C-56E0CFB6E612}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21831,24 +21853,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
   <ds:schemaRefs>

--- a/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BCDTRtSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29373D27-92E1-4836-A190-6D1BDD6A0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D07F60B-7C55-4352-AC4E-D272D80DA40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4347" yWindow="761" windowWidth="17661" windowHeight="11289" tabRatio="742" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2486" yWindow="3233" windowWidth="17660" windowHeight="11289" tabRatio="742" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="33" r:id="rId1"/>
@@ -1088,7 +1088,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1267,6 +1267,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1920,7 +1926,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2082,9 +2088,6 @@
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2096,6 +2099,9 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2127,6 +2133,7 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2963,81 +2970,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="H1" s="70" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="H1" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
       <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="67" t="s">
         <v>80</v>
       </c>
       <c r="G2" s="53"/>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="68" t="s">
+      <c r="J2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="68" t="s">
+      <c r="L2" s="67" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="41"/>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="67" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
       <c r="G3" s="53"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
       <c r="M3" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="68"/>
+      <c r="N3" s="67"/>
     </row>
     <row r="4" spans="1:21" ht="13.6" customHeight="1">
       <c r="A4" s="42" t="s">
@@ -3161,14 +3168,14 @@
       <c r="N6" s="44">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="66" t="s">
+      <c r="P6" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="66"/>
-      <c r="U6" s="66"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
     </row>
     <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="42" t="s">
@@ -3210,18 +3217,18 @@
       <c r="N7" s="44">
         <v>8.18</v>
       </c>
-      <c r="P7" s="67"/>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="67" t="s">
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="67" t="s">
+      <c r="S7" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="T7" s="67" t="s">
+      <c r="T7" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="67" t="s">
+      <c r="U7" s="66" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3265,12 +3272,12 @@
       <c r="N8" s="44">
         <v>10.1</v>
       </c>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="67"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
     </row>
     <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="42" t="s">
@@ -3988,10 +3995,10 @@
         <v>71.8</v>
       </c>
       <c r="P21" s="56"/>
-      <c r="Q21" s="67" t="s">
+      <c r="Q21" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="67"/>
+      <c r="R21" s="66"/>
       <c r="S21" s="55" cm="1">
         <f t="array" ref="S21:V24">TRANSPOSE(R9:U12)</f>
         <v>1</v>
@@ -4051,10 +4058,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P22" s="56"/>
-      <c r="Q22" s="67" t="s">
+      <c r="Q22" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="67"/>
+      <c r="R22" s="66"/>
       <c r="S22" s="55">
         <v>1</v>
       </c>
@@ -4113,10 +4120,10 @@
         <v>94.275260000000003</v>
       </c>
       <c r="P23" s="56"/>
-      <c r="Q23" s="67" t="s">
+      <c r="Q23" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="R23" s="67"/>
+      <c r="R23" s="66"/>
       <c r="S23" s="55">
         <v>1</v>
       </c>
@@ -4175,10 +4182,10 @@
         <v>116.386674</v>
       </c>
       <c r="P24" s="56"/>
-      <c r="Q24" s="67" t="s">
+      <c r="Q24" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="R24" s="67"/>
+      <c r="R24" s="66"/>
       <c r="S24" s="55">
         <v>1</v>
       </c>
@@ -4338,10 +4345,10 @@
       <c r="N27" s="44">
         <v>178.89815999999999</v>
       </c>
-      <c r="Q27" s="67" t="s">
+      <c r="Q27" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="67"/>
+      <c r="R27" s="66"/>
       <c r="S27" s="55" cm="1">
         <f t="array" ref="S27:V30">TRANSPOSE(R13:U16)</f>
         <v>1</v>
@@ -4396,10 +4403,10 @@
       <c r="N28" s="44">
         <v>173.91</v>
       </c>
-      <c r="Q28" s="67" t="s">
+      <c r="Q28" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="67"/>
+      <c r="R28" s="66"/>
       <c r="S28" s="55">
         <v>1</v>
       </c>
@@ -4453,10 +4460,10 @@
       <c r="N29" s="44">
         <v>163.88936200000001</v>
       </c>
-      <c r="Q29" s="67" t="s">
+      <c r="Q29" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="R29" s="67"/>
+      <c r="R29" s="66"/>
       <c r="S29" s="55">
         <v>1</v>
       </c>
@@ -4510,10 +4517,10 @@
       <c r="N30" s="44">
         <v>170.29181</v>
       </c>
-      <c r="Q30" s="67" t="s">
+      <c r="Q30" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="R30" s="67"/>
+      <c r="R30" s="66"/>
       <c r="S30" s="55">
         <v>1</v>
       </c>
@@ -5113,16 +5120,17 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
@@ -5134,17 +5142,16 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
   </mergeCells>
   <phoneticPr fontId="44" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19378,132 +19385,132 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <f>passenger!F36</f>
-        <v>0.93176953330484824</v>
+        <f>passenger!F36*1.05</f>
+        <v>0.9783580099700907</v>
       </c>
       <c r="D2">
-        <f>passenger!G36*0.975</f>
-        <v>0.9608096724998636</v>
+        <f>passenger!G36*1.05</f>
+        <v>1.0347181088460071</v>
       </c>
       <c r="E2">
-        <f>passenger!H36</f>
-        <v>0.95487307061576332</v>
+        <f>passenger!H36*1.02</f>
+        <v>0.97397053202807859</v>
       </c>
       <c r="F2">
-        <f>passenger!I36</f>
-        <v>0.92847419815695842</v>
+        <f>passenger!I36*1.4</f>
+        <v>1.2998638774197417</v>
       </c>
       <c r="G2">
-        <f>passenger!J36</f>
-        <v>0.91612681141496144</v>
+        <f>passenger!J36*1.4</f>
+        <v>1.2825775359809459</v>
       </c>
       <c r="H2">
-        <f>passenger!K36</f>
-        <v>0.9639065212252057</v>
+        <f>passenger!K36*1.4</f>
+        <v>1.3494691297152879</v>
       </c>
       <c r="I2">
-        <f>passenger!L36</f>
-        <v>1.007687069095907</v>
+        <f>passenger!L36*1.35</f>
+        <v>1.3603775432794745</v>
       </c>
       <c r="J2">
-        <f>passenger!M36</f>
-        <v>1.0411015680975508</v>
+        <f>passenger!M36*1.34</f>
+        <v>1.3950761012507182</v>
       </c>
       <c r="K2">
-        <f>passenger!N36</f>
-        <v>1.0674045241183117</v>
+        <f>passenger!N36*1.32</f>
+        <v>1.4089739718361713</v>
       </c>
       <c r="L2">
-        <f>passenger!O36</f>
-        <v>1.0885588949344038</v>
+        <f>passenger!O36*1.3</f>
+        <v>1.415126563414725</v>
       </c>
       <c r="M2">
-        <f>passenger!P36</f>
-        <v>1.1069691399758801</v>
+        <f>passenger!P36*1.28</f>
+        <v>1.4169204991691264</v>
       </c>
       <c r="N2">
-        <f>passenger!Q36</f>
-        <v>1.1222554793931736</v>
+        <f>passenger!Q36*1.27</f>
+        <v>1.4252644588293304</v>
       </c>
       <c r="O2">
-        <f>passenger!R36</f>
-        <v>1.1360718178150595</v>
+        <f>passenger!R36*1.26</f>
+        <v>1.4314504904469749</v>
       </c>
       <c r="P2">
-        <f>passenger!S36</f>
-        <v>1.1477068418857206</v>
+        <f>passenger!S36*1.25</f>
+        <v>1.4346335523571507</v>
       </c>
       <c r="Q2">
-        <f>passenger!T36</f>
-        <v>1.1571701293353269</v>
+        <f>passenger!T36*1.24</f>
+        <v>1.4348909603758053</v>
       </c>
       <c r="R2">
-        <f>passenger!U36</f>
-        <v>1.1641104214519824</v>
+        <f>passenger!U36*1.23</f>
+        <v>1.4318558183859382</v>
       </c>
       <c r="S2">
-        <f>passenger!V36</f>
-        <v>1.1695724791191184</v>
+        <f>passenger!V36*1.22</f>
+        <v>1.4268784245253245</v>
       </c>
       <c r="T2">
-        <f>passenger!W36</f>
-        <v>1.1729195343857188</v>
+        <f>passenger!W36*1.21</f>
+        <v>1.4192326366067198</v>
       </c>
       <c r="U2">
-        <f>passenger!X36</f>
-        <v>1.1744435698424076</v>
+        <f>passenger!X36*1.2</f>
+        <v>1.409332283810889</v>
       </c>
       <c r="V2">
-        <f>passenger!Y36</f>
-        <v>1.1743052991837069</v>
+        <f>passenger!Y36*1.19</f>
+        <v>1.3974233060286112</v>
       </c>
       <c r="W2">
-        <f>passenger!Z36</f>
-        <v>1.1726448868461425</v>
+        <f>passenger!Z36*1.18</f>
+        <v>1.3837209664784482</v>
       </c>
       <c r="X2">
-        <f>passenger!AA36</f>
-        <v>1.1697033499117306</v>
+        <f>passenger!AA36*1.17</f>
+        <v>1.3685529193967247</v>
       </c>
       <c r="Y2">
-        <f>passenger!AB36</f>
-        <v>1.1654578178816104</v>
+        <f>passenger!AB36*1.16</f>
+        <v>1.351931068742668</v>
       </c>
       <c r="Z2">
-        <f>passenger!AC36</f>
-        <v>1.1600214360864807</v>
+        <f>passenger!AC36*1.15</f>
+        <v>1.3340246514994527</v>
       </c>
       <c r="AA2">
-        <f>passenger!AD36</f>
-        <v>1.1535097225613236</v>
+        <f>passenger!AD36*1.14</f>
+        <v>1.3150010837199086</v>
       </c>
       <c r="AB2">
-        <f>passenger!AE36</f>
-        <v>1.1460124350708616</v>
+        <f>passenger!AE36*1.13</f>
+        <v>1.2949940516300735</v>
       </c>
       <c r="AC2">
-        <f>passenger!AF36</f>
-        <v>1.1376748785825224</v>
+        <f>passenger!AF36*1.12</f>
+        <v>1.2741958640124251</v>
       </c>
       <c r="AD2">
-        <f>passenger!AG36</f>
-        <v>1.1285095131661682</v>
+        <f>passenger!AG36*1.1</f>
+        <v>1.2413604644827851</v>
       </c>
       <c r="AE2">
-        <f>passenger!AH36</f>
-        <v>1.1185986129913399</v>
+        <f>passenger!AH36*1.08</f>
+        <v>1.2080865020306473</v>
       </c>
       <c r="AF2">
-        <f>passenger!AI36</f>
-        <v>1.108042685107397</v>
+        <f>passenger!AI36*1.06</f>
+        <v>1.1745252462138409</v>
       </c>
       <c r="AG2">
-        <f>passenger!AJ36</f>
-        <v>1.0969208380030395</v>
+        <f>passenger!AJ36*1.04</f>
+        <v>1.1407976715231611</v>
       </c>
       <c r="AH2">
-        <f>passenger!AK36</f>
-        <v>1.0854850327805792</v>
+        <f>passenger!AK36*1.1</f>
+        <v>1.1940335360586372</v>
       </c>
       <c r="AI2">
         <f>passenger!AL36</f>
@@ -19566,15 +19573,15 @@
         <f>passenger!I38</f>
         <v>0.76400637311512787</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="81">
         <f>passenger!J38</f>
         <v>0.76112540281291752</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="81">
         <f>passenger!K38</f>
         <v>0.75782468436877115</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="81">
         <f>passenger!L38</f>
         <v>0.75462803352260688</v>
       </c>
@@ -21564,12 +21571,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21807,28 +21814,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21854,9 +21851,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/cn-BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BCDTRtSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D07F60B-7C55-4352-AC4E-D272D80DA40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6283F4-B7BC-423A-B6F1-5020F231D11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2486" yWindow="3233" windowWidth="17660" windowHeight="11289" tabRatio="742" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8314" yWindow="1114" windowWidth="17660" windowHeight="11289" tabRatio="742" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="33" r:id="rId1"/>
@@ -2085,8 +2085,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="155" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2099,9 +2103,6 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2133,7 +2134,6 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2970,81 +2970,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="H1" s="69" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="H1" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
       <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="69" t="s">
         <v>80</v>
       </c>
       <c r="G2" s="53"/>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="67" t="s">
+      <c r="J2" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="67" t="s">
+      <c r="K2" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="67" t="s">
+      <c r="L2" s="69" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="41"/>
-      <c r="N2" s="67" t="s">
+      <c r="N2" s="69" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="39" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
       <c r="G3" s="53"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
       <c r="M3" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="67"/>
+      <c r="N3" s="69"/>
     </row>
     <row r="4" spans="1:21" ht="13.6" customHeight="1">
       <c r="A4" s="42" t="s">
@@ -3168,14 +3168,14 @@
       <c r="N6" s="44">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
     </row>
     <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="42" t="s">
@@ -3217,18 +3217,18 @@
       <c r="N7" s="44">
         <v>8.18</v>
       </c>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66" t="s">
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="66" t="s">
+      <c r="S7" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="T7" s="66" t="s">
+      <c r="T7" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="66" t="s">
+      <c r="U7" s="68" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       <c r="N8" s="44">
         <v>10.1</v>
       </c>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="66"/>
-      <c r="U8" s="66"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="68"/>
     </row>
     <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="42" t="s">
@@ -3319,7 +3319,7 @@
       <c r="N9" s="44">
         <v>13.42</v>
       </c>
-      <c r="P9" s="65" t="s">
+      <c r="P9" s="66" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="54">
@@ -3378,7 +3378,7 @@
       <c r="N10" s="44">
         <v>16.61</v>
       </c>
-      <c r="P10" s="65"/>
+      <c r="P10" s="66"/>
       <c r="Q10" s="54">
         <v>2020</v>
       </c>
@@ -3439,7 +3439,7 @@
       <c r="N11" s="44">
         <v>18.579999999999998</v>
       </c>
-      <c r="P11" s="65"/>
+      <c r="P11" s="66"/>
       <c r="Q11" s="54">
         <v>2021</v>
       </c>
@@ -3500,7 +3500,7 @@
       <c r="N12" s="44">
         <v>22.3</v>
       </c>
-      <c r="P12" s="65"/>
+      <c r="P12" s="66"/>
       <c r="Q12" s="54">
         <v>2022</v>
       </c>
@@ -3561,7 +3561,7 @@
       <c r="N13" s="44">
         <v>24.93</v>
       </c>
-      <c r="P13" s="65" t="s">
+      <c r="P13" s="66" t="s">
         <v>83</v>
       </c>
       <c r="Q13" s="54">
@@ -3620,7 +3620,7 @@
       <c r="N14" s="44">
         <v>29.1</v>
       </c>
-      <c r="P14" s="65"/>
+      <c r="P14" s="66"/>
       <c r="Q14" s="54">
         <v>2020</v>
       </c>
@@ -3681,7 +3681,7 @@
       <c r="N15" s="44">
         <v>33.450000000000003</v>
       </c>
-      <c r="P15" s="65"/>
+      <c r="P15" s="66"/>
       <c r="Q15" s="54">
         <v>2021</v>
       </c>
@@ -3742,7 +3742,7 @@
       <c r="N16" s="44">
         <v>42.34</v>
       </c>
-      <c r="P16" s="65"/>
+      <c r="P16" s="66"/>
       <c r="Q16" s="54">
         <v>2022</v>
       </c>
@@ -3886,14 +3886,14 @@
         <v>51.55</v>
       </c>
       <c r="P19" s="56"/>
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="66"/>
+      <c r="V19" s="66"/>
     </row>
     <row r="20" spans="1:23" ht="13.6" customHeight="1">
       <c r="A20" s="42" t="s">
@@ -3995,10 +3995,10 @@
         <v>71.8</v>
       </c>
       <c r="P21" s="56"/>
-      <c r="Q21" s="66" t="s">
+      <c r="Q21" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="66"/>
+      <c r="R21" s="68"/>
       <c r="S21" s="55" cm="1">
         <f t="array" ref="S21:V24">TRANSPOSE(R9:U12)</f>
         <v>1</v>
@@ -4058,10 +4058,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P22" s="56"/>
-      <c r="Q22" s="66" t="s">
+      <c r="Q22" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="66"/>
+      <c r="R22" s="68"/>
       <c r="S22" s="55">
         <v>1</v>
       </c>
@@ -4120,10 +4120,10 @@
         <v>94.275260000000003</v>
       </c>
       <c r="P23" s="56"/>
-      <c r="Q23" s="66" t="s">
+      <c r="Q23" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="R23" s="66"/>
+      <c r="R23" s="68"/>
       <c r="S23" s="55">
         <v>1</v>
       </c>
@@ -4182,10 +4182,10 @@
         <v>116.386674</v>
       </c>
       <c r="P24" s="56"/>
-      <c r="Q24" s="66" t="s">
+      <c r="Q24" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="R24" s="66"/>
+      <c r="R24" s="68"/>
       <c r="S24" s="55">
         <v>1</v>
       </c>
@@ -4243,14 +4243,14 @@
       <c r="N25" s="44">
         <v>119.602272</v>
       </c>
-      <c r="Q25" s="65" t="s">
+      <c r="Q25" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
     </row>
     <row r="26" spans="1:23" ht="13.6" customHeight="1">
       <c r="A26" s="42">
@@ -4345,10 +4345,10 @@
       <c r="N27" s="44">
         <v>178.89815999999999</v>
       </c>
-      <c r="Q27" s="66" t="s">
+      <c r="Q27" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="66"/>
+      <c r="R27" s="68"/>
       <c r="S27" s="55" cm="1">
         <f t="array" ref="S27:V30">TRANSPOSE(R13:U16)</f>
         <v>1</v>
@@ -4403,10 +4403,10 @@
       <c r="N28" s="44">
         <v>173.91</v>
       </c>
-      <c r="Q28" s="66" t="s">
+      <c r="Q28" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="66"/>
+      <c r="R28" s="68"/>
       <c r="S28" s="55">
         <v>1</v>
       </c>
@@ -4460,10 +4460,10 @@
       <c r="N29" s="44">
         <v>163.88936200000001</v>
       </c>
-      <c r="Q29" s="66" t="s">
+      <c r="Q29" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="R29" s="66"/>
+      <c r="R29" s="68"/>
       <c r="S29" s="55">
         <v>1</v>
       </c>
@@ -4517,10 +4517,10 @@
       <c r="N30" s="44">
         <v>170.29181</v>
       </c>
-      <c r="Q30" s="66" t="s">
+      <c r="Q30" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="R30" s="66"/>
+      <c r="R30" s="68"/>
       <c r="S30" s="55">
         <v>1</v>
       </c>
@@ -5120,17 +5120,16 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
@@ -5142,16 +5141,17 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
   </mergeCells>
   <phoneticPr fontId="44" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5171,10 +5171,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="14.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="74"/>
+      <c r="B1" s="75"/>
       <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
@@ -5402,10 +5402,10 @@
       </c>
     </row>
     <row r="2" spans="1:77" ht="14.3">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="72"/>
+      <c r="B2" s="73"/>
       <c r="C2" s="11"/>
       <c r="D2" s="12">
         <v>1743.1</v>
@@ -5517,10 +5517,10 @@
       </c>
     </row>
     <row r="3" spans="1:77" ht="14.3">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="72"/>
+      <c r="B3" s="73"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9">
         <v>1093.22</v>
@@ -5782,10 +5782,10 @@
       </c>
     </row>
     <row r="4" spans="1:77" ht="14.3">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="72"/>
+      <c r="B4" s="73"/>
       <c r="C4" s="7"/>
       <c r="D4" s="9">
         <v>521.29999999999995</v>
@@ -6047,10 +6047,10 @@
       </c>
     </row>
     <row r="5" spans="1:77" ht="14.3">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="72"/>
+      <c r="B5" s="73"/>
       <c r="C5" s="7"/>
       <c r="D5" s="9">
         <v>100.63</v>
@@ -12386,11 +12386,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="14.95" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
       <c r="D1" s="22" t="s">
         <v>27</v>
       </c>
@@ -12615,11 +12615,11 @@
       </c>
     </row>
     <row r="2" spans="1:77" ht="15.65" customHeight="1" thickBot="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="13">
         <v>9928</v>
       </c>
@@ -12730,11 +12730,11 @@
       </c>
     </row>
     <row r="3" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
       <c r="D3" s="9">
         <v>5345.19</v>
       </c>
@@ -12995,11 +12995,11 @@
       </c>
     </row>
     <row r="4" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="9">
         <v>350.3</v>
       </c>
@@ -13260,11 +13260,11 @@
       </c>
     </row>
     <row r="5" spans="1:77" ht="16.3" thickBot="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
       <c r="D5" s="9">
         <v>3801.8</v>
       </c>
@@ -13526,10 +13526,10 @@
     </row>
     <row r="6" spans="1:77" ht="16.3" thickBot="1">
       <c r="A6" s="27"/>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="72"/>
+      <c r="C6" s="73"/>
       <c r="D6" s="14">
         <v>2487</v>
       </c>
@@ -19385,132 +19385,132 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <f>passenger!F36*1.05</f>
-        <v>0.9783580099700907</v>
+        <f>passenger!F36</f>
+        <v>0.93176953330484824</v>
       </c>
       <c r="D2">
-        <f>passenger!G36*1.05</f>
-        <v>1.0347181088460071</v>
+        <f>passenger!G36</f>
+        <v>0.98544581794857811</v>
       </c>
       <c r="E2">
-        <f>passenger!H36*1.02</f>
-        <v>0.97397053202807859</v>
+        <f>passenger!H36</f>
+        <v>0.95487307061576332</v>
       </c>
       <c r="F2">
-        <f>passenger!I36*1.4</f>
-        <v>1.2998638774197417</v>
+        <f>passenger!I36*1.2</f>
+        <v>1.11416903778835</v>
       </c>
       <c r="G2">
-        <f>passenger!J36*1.4</f>
-        <v>1.2825775359809459</v>
+        <f>passenger!J36*1.25</f>
+        <v>1.1451585142687017</v>
       </c>
       <c r="H2">
-        <f>passenger!K36*1.4</f>
-        <v>1.3494691297152879</v>
+        <f>passenger!K36*1.26</f>
+        <v>1.2145222167437593</v>
       </c>
       <c r="I2">
-        <f>passenger!L36*1.35</f>
-        <v>1.3603775432794745</v>
+        <f>passenger!L36*1.25</f>
+        <v>1.2596088363698836</v>
       </c>
       <c r="J2">
-        <f>passenger!M36*1.34</f>
-        <v>1.3950761012507182</v>
+        <f>passenger!M36*1.25</f>
+        <v>1.3013769601219385</v>
       </c>
       <c r="K2">
-        <f>passenger!N36*1.32</f>
-        <v>1.4089739718361713</v>
+        <f>passenger!N36*1.25</f>
+        <v>1.3342556551478895</v>
       </c>
       <c r="L2">
-        <f>passenger!O36*1.3</f>
-        <v>1.415126563414725</v>
+        <f>passenger!O36*1.25</f>
+        <v>1.3606986186680048</v>
       </c>
       <c r="M2">
-        <f>passenger!P36*1.28</f>
-        <v>1.4169204991691264</v>
+        <f>passenger!P36*1.25</f>
+        <v>1.3837114249698501</v>
       </c>
       <c r="N2">
-        <f>passenger!Q36*1.27</f>
-        <v>1.4252644588293304</v>
+        <f>passenger!Q36*1.24</f>
+        <v>1.3915967944475354</v>
       </c>
       <c r="O2">
-        <f>passenger!R36*1.26</f>
-        <v>1.4314504904469749</v>
+        <f>passenger!R36*1.225</f>
+        <v>1.391687976823448</v>
       </c>
       <c r="P2">
-        <f>passenger!S36*1.25</f>
-        <v>1.4346335523571507</v>
+        <f>passenger!S36*1.21</f>
+        <v>1.3887252786817219</v>
       </c>
       <c r="Q2">
-        <f>passenger!T36*1.24</f>
-        <v>1.4348909603758053</v>
+        <f>passenger!T36*1.19</f>
+        <v>1.3770324539090391</v>
       </c>
       <c r="R2">
-        <f>passenger!U36*1.23</f>
-        <v>1.4318558183859382</v>
+        <f>passenger!U36*1.17</f>
+        <v>1.3620091930988194</v>
       </c>
       <c r="S2">
-        <f>passenger!V36*1.22</f>
-        <v>1.4268784245253245</v>
+        <f>passenger!V36*1.153</f>
+        <v>1.3485170684243435</v>
       </c>
       <c r="T2">
-        <f>passenger!W36*1.21</f>
-        <v>1.4192326366067198</v>
+        <f>passenger!W36*1.13</f>
+        <v>1.3253990738558621</v>
       </c>
       <c r="U2">
-        <f>passenger!X36*1.2</f>
-        <v>1.409332283810889</v>
+        <f>passenger!X36*1.105</f>
+        <v>1.2977601446758604</v>
       </c>
       <c r="V2">
-        <f>passenger!Y36*1.19</f>
-        <v>1.3974233060286112</v>
+        <f>passenger!Y36*1.08</f>
+        <v>1.2682497231184036</v>
       </c>
       <c r="W2">
-        <f>passenger!Z36*1.18</f>
-        <v>1.3837209664784482</v>
+        <f>passenger!Z36*1.05</f>
+        <v>1.2312771311884496</v>
       </c>
       <c r="X2">
-        <f>passenger!AA36*1.17</f>
-        <v>1.3685529193967247</v>
+        <f>passenger!AA36*1.02</f>
+        <v>1.1930974169099653</v>
       </c>
       <c r="Y2">
-        <f>passenger!AB36*1.16</f>
-        <v>1.351931068742668</v>
+        <f>passenger!AB36*1.01</f>
+        <v>1.1771123960604266</v>
       </c>
       <c r="Z2">
-        <f>passenger!AC36*1.15</f>
-        <v>1.3340246514994527</v>
+        <f>passenger!AC36</f>
+        <v>1.1600214360864807</v>
       </c>
       <c r="AA2">
-        <f>passenger!AD36*1.14</f>
-        <v>1.3150010837199086</v>
+        <f>passenger!AD36</f>
+        <v>1.1535097225613236</v>
       </c>
       <c r="AB2">
-        <f>passenger!AE36*1.13</f>
-        <v>1.2949940516300735</v>
+        <f>passenger!AE36</f>
+        <v>1.1460124350708616</v>
       </c>
       <c r="AC2">
-        <f>passenger!AF36*1.12</f>
-        <v>1.2741958640124251</v>
+        <f>passenger!AF36</f>
+        <v>1.1376748785825224</v>
       </c>
       <c r="AD2">
-        <f>passenger!AG36*1.1</f>
-        <v>1.2413604644827851</v>
+        <f>passenger!AG36</f>
+        <v>1.1285095131661682</v>
       </c>
       <c r="AE2">
-        <f>passenger!AH36*1.08</f>
-        <v>1.2080865020306473</v>
+        <f>passenger!AH36</f>
+        <v>1.1185986129913399</v>
       </c>
       <c r="AF2">
-        <f>passenger!AI36*1.06</f>
-        <v>1.1745252462138409</v>
+        <f>passenger!AI36</f>
+        <v>1.108042685107397</v>
       </c>
       <c r="AG2">
-        <f>passenger!AJ36*1.04</f>
-        <v>1.1407976715231611</v>
+        <f>passenger!AJ36</f>
+        <v>1.0969208380030395</v>
       </c>
       <c r="AH2">
-        <f>passenger!AK36*1.1</f>
-        <v>1.1940335360586372</v>
+        <f>passenger!AK36</f>
+        <v>1.0854850327805792</v>
       </c>
       <c r="AI2">
         <f>passenger!AL36</f>
@@ -19573,15 +19573,15 @@
         <f>passenger!I38</f>
         <v>0.76400637311512787</v>
       </c>
-      <c r="G3" s="81">
+      <c r="G3" s="65">
         <f>passenger!J38</f>
         <v>0.76112540281291752</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="65">
         <f>passenger!K38</f>
         <v>0.75782468436877115</v>
       </c>
-      <c r="I3" s="81">
+      <c r="I3" s="65">
         <f>passenger!L38</f>
         <v>0.75462803352260688</v>
       </c>
@@ -19759,140 +19759,140 @@
         <v>1.350581414143956</v>
       </c>
       <c r="J4">
-        <f>passenger!M30*1.04</f>
-        <v>1.4592560866260185</v>
+        <f>passenger!M30*1.03</f>
+        <v>1.4452247781007683</v>
       </c>
       <c r="K4">
-        <f>passenger!N30*1.06</f>
-        <v>1.5760921878438274</v>
+        <f>passenger!N30*1.04</f>
+        <v>1.546354599393944</v>
       </c>
       <c r="L4">
-        <f>passenger!O30*1.08</f>
-        <v>1.7016768223026257</v>
+        <f>passenger!O30*1.045</f>
+        <v>1.646529888246522</v>
       </c>
       <c r="M4">
-        <f>passenger!P30*1.1</f>
-        <v>1.836638104106687</v>
+        <f>passenger!P30*1.055</f>
+        <v>1.761502908938686</v>
       </c>
       <c r="N4">
-        <f>passenger!Q30*1.15</f>
-        <v>2.0023180722773808</v>
+        <f>passenger!Q30*1.07</f>
+        <v>1.8630263802928675</v>
       </c>
       <c r="O4">
-        <f>passenger!R30*1.14</f>
-        <v>2.069876338126575</v>
+        <f>passenger!R30*1.03</f>
+        <v>1.8701514283073442</v>
       </c>
       <c r="P4">
-        <f>passenger!S30*1.1</f>
-        <v>2.0827471817778784</v>
+        <f>passenger!S30</f>
+        <v>1.8934065288889803</v>
       </c>
       <c r="Q4">
-        <f>passenger!T30*1.06</f>
-        <v>2.0929268875409308</v>
+        <f>passenger!T30</f>
+        <v>1.9744593278688025</v>
       </c>
       <c r="R4">
-        <f>passenger!U30*1.02</f>
-        <v>2.100161465319129</v>
+        <f>passenger!U30</f>
+        <v>2.0589818287442441</v>
       </c>
       <c r="S4">
-        <f>passenger!V30*1.02</f>
-        <v>2.1070008350032232</v>
+        <f>passenger!V30</f>
+        <v>2.065687093140415</v>
       </c>
       <c r="T4">
-        <f>passenger!W30*1.015</f>
-        <v>2.1035004067568117</v>
+        <f>passenger!W30</f>
+        <v>2.0724141938490757</v>
       </c>
       <c r="U4">
-        <f>passenger!X30*1.01</f>
-        <v>2.0999548340020144</v>
+        <f>passenger!X30</f>
+        <v>2.0791632019821926</v>
       </c>
       <c r="V4">
-        <f>passenger!Y30*1.01</f>
-        <v>2.1067935307721499</v>
+        <f>passenger!Y30</f>
+        <v>2.0859341888833169</v>
       </c>
       <c r="W4">
-        <f>passenger!Z30*1.01</f>
-        <v>2.1136544983896184</v>
+        <f>passenger!Z30</f>
+        <v>2.0927272261283352</v>
       </c>
       <c r="X4">
-        <f>passenger!AA30*1.01</f>
-        <v>2.1247206421089015</v>
+        <f>passenger!AA30</f>
+        <v>2.1036838040682193</v>
       </c>
       <c r="Y4">
-        <f>passenger!AB30*1.01</f>
-        <v>2.1358447231764641</v>
+        <f>passenger!AB30</f>
+        <v>2.1146977457192713</v>
       </c>
       <c r="Z4">
-        <f>passenger!AC30*1.01</f>
-        <v>2.1470270449261877</v>
+        <f>passenger!AC30</f>
+        <v>2.125769351412067</v>
       </c>
       <c r="AA4">
-        <f>passenger!AD30*1.01</f>
-        <v>2.1582679122800736</v>
+        <f>passenger!AD30</f>
+        <v>2.1368989230495776</v>
       </c>
       <c r="AB4">
-        <f>passenger!AE30*1.01</f>
-        <v>2.1695676317565549</v>
+        <f>passenger!AE30</f>
+        <v>2.1480867641154009</v>
       </c>
       <c r="AC4">
-        <f>passenger!AF30*1.01</f>
-        <v>2.1553879499100379</v>
+        <f>passenger!AF30</f>
+        <v>2.1340474751584533</v>
       </c>
       <c r="AD4">
-        <f>passenger!AG30*1.01</f>
-        <v>2.1413009424629381</v>
+        <f>passenger!AG30</f>
+        <v>2.1200999430326122</v>
       </c>
       <c r="AE4">
-        <f>passenger!AH30*1.01</f>
-        <v>2.1273060037215323</v>
+        <f>passenger!AH30</f>
+        <v>2.1062435680411209</v>
       </c>
       <c r="AF4">
-        <f>passenger!AI30*1.01</f>
-        <v>2.1134025319507375</v>
+        <f>passenger!AI30</f>
+        <v>2.0924777544066706</v>
       </c>
       <c r="AG4">
-        <f>passenger!AJ30*1.01</f>
-        <v>2.0995899293482441</v>
+        <f>passenger!AJ30</f>
+        <v>2.0788019102457862</v>
       </c>
       <c r="AH4">
-        <f>passenger!AK30*1.01</f>
-        <v>2.0523116786057041</v>
+        <f>passenger!AK30</f>
+        <v>2.0319917609957465</v>
       </c>
       <c r="AI4">
-        <f>passenger!AL30*1.01</f>
-        <v>2.0060980324138105</v>
+        <f>passenger!AL30</f>
+        <v>1.9862356756572381</v>
       </c>
       <c r="AJ4">
-        <f>passenger!AM30*1.01</f>
-        <v>1.9609250181671583</v>
+        <f>passenger!AM30</f>
+        <v>1.9415099189773843</v>
       </c>
       <c r="AK4">
-        <f>passenger!AN30*1.01</f>
-        <v>1.9167692030718722</v>
+        <f>passenger!AN30</f>
+        <v>1.8977912901701703</v>
       </c>
       <c r="AL4">
-        <f>passenger!AO30*1.01</f>
-        <v>1.8736076819902099</v>
+        <f>passenger!AO30</f>
+        <v>1.8550571108813958</v>
       </c>
       <c r="AM4">
-        <f>passenger!AP30*1.01</f>
-        <v>1.8141804595535331</v>
+        <f>passenger!AP30</f>
+        <v>1.7962182767856762</v>
       </c>
       <c r="AN4">
-        <f>passenger!AQ30*1.01</f>
-        <v>1.7566381540076681</v>
+        <f>passenger!AQ30</f>
+        <v>1.7392456970372951</v>
       </c>
       <c r="AO4">
-        <f>passenger!AR30*1.01</f>
-        <v>1.7009209794238844</v>
+        <f>passenger!AR30</f>
+        <v>1.6840801776474104</v>
       </c>
       <c r="AP4">
-        <f>passenger!AS30*1.01</f>
-        <v>1.6469710461678138</v>
+        <f>passenger!AS30</f>
+        <v>1.6306644021463503</v>
       </c>
       <c r="AQ4">
-        <f>passenger!AT30*1.01</f>
-        <v>1.5947323007526506</v>
+        <f>passenger!AT30</f>
+        <v>1.5789428720323273</v>
       </c>
     </row>
     <row r="5" spans="1:43">
@@ -20900,48 +20900,48 @@
         <v>1.3984176791404332</v>
       </c>
       <c r="I4">
-        <f>freight!L32*1.02</f>
-        <v>1.4819836471950065</v>
+        <f>freight!L32</f>
+        <v>1.4529251443088298</v>
       </c>
       <c r="J4">
-        <f>freight!M32*1.04</f>
-        <v>1.5594219166732097</v>
+        <f>freight!M32*1.005</f>
+        <v>1.5069413714005535</v>
       </c>
       <c r="K4">
-        <f>freight!N32*1.06</f>
-        <v>1.6330486094795564</v>
+        <f>freight!N32*1.008</f>
+        <v>1.5529367909013139</v>
       </c>
       <c r="L4">
-        <f>freight!O32*1.08</f>
-        <v>1.7043469127667845</v>
+        <f>freight!O32*1.01</f>
+        <v>1.5938799832356041</v>
       </c>
       <c r="M4">
-        <f>freight!P32*1.1</f>
-        <v>1.7768072906740804</v>
+        <f>freight!P32*1.022</f>
+        <v>1.6508155009717365</v>
       </c>
       <c r="N4">
-        <f>freight!Q32*1.12</f>
-        <v>1.8492162726981716</v>
+        <f>freight!Q32*1.025</f>
+        <v>1.6923631067103799</v>
       </c>
       <c r="O4">
-        <f>freight!R32*1.1</f>
-        <v>1.8577381242923523</v>
+        <f>freight!R32*1.015</f>
+        <v>1.7141856328697611</v>
       </c>
       <c r="P4">
-        <f>freight!S32*1.08</f>
-        <v>1.8652919917105339</v>
+        <f>freight!S32*1.01</f>
+        <v>1.7443934366922584</v>
       </c>
       <c r="Q4">
-        <f>freight!T32*1.06</f>
-        <v>1.8716789463530799</v>
+        <f>freight!T32</f>
+        <v>1.7657348550500753</v>
       </c>
       <c r="R4">
-        <f>freight!U32*1.04</f>
-        <v>1.8761182774104475</v>
+        <f>freight!U32</f>
+        <v>1.8039598821254301</v>
       </c>
       <c r="S4">
-        <f>freight!V32*1.02</f>
-        <v>1.8812772138251508</v>
+        <f>freight!V32</f>
+        <v>1.8443894253187751</v>
       </c>
       <c r="T4">
         <f>freight!W32</f>
@@ -21246,76 +21246,76 @@
         <v>1.3952928673681615</v>
       </c>
       <c r="I6">
-        <f>freight!L37*1.02</f>
-        <v>1.4489910441130174</v>
+        <f>freight!L37</f>
+        <v>1.4205794550127622</v>
       </c>
       <c r="J6">
-        <f>freight!M37*1.04</f>
-        <v>1.5041772781962843</v>
+        <f>freight!M37*1.005</f>
+        <v>1.4535559274877552</v>
       </c>
       <c r="K6">
-        <f>freight!N37*1.06</f>
-        <v>1.5608878687219636</v>
+        <f>freight!N37*1.005</f>
+        <v>1.4798984038354464</v>
       </c>
       <c r="L6">
-        <f>freight!O37*1.08</f>
-        <v>1.6191599417450919</v>
+        <f>freight!O37*1.008</f>
+        <v>1.5112159456287524</v>
       </c>
       <c r="M6">
-        <f>freight!P37*1.1</f>
-        <v>1.6790314683231444</v>
+        <f>freight!P37*1.015</f>
+        <v>1.5492881275890831</v>
       </c>
       <c r="N6">
-        <f>freight!Q37*1.12</f>
-        <v>1.7332492200881424</v>
+        <f>freight!Q37*1.015</f>
+        <v>1.5707571057048786</v>
       </c>
       <c r="O6">
-        <f>freight!R37*1.11</f>
-        <v>1.7415775179959707</v>
+        <f>freight!R37*1.008</f>
+        <v>1.5815406649909354</v>
       </c>
       <c r="P6">
-        <f>freight!S37*1.1</f>
-        <v>1.7498038040158228</v>
+        <f>freight!S37</f>
+        <v>1.5907307309234751</v>
       </c>
       <c r="Q6">
-        <f>freight!T37*1.08</f>
-        <v>1.7417959117581199</v>
+        <f>freight!T37</f>
+        <v>1.6127739923686295</v>
       </c>
       <c r="R6">
-        <f>freight!U37*1.07</f>
-        <v>1.7495813042960442</v>
+        <f>freight!U37</f>
+        <v>1.6351227142953684</v>
       </c>
       <c r="S6">
-        <f>freight!V37*1.06</f>
-        <v>1.7551331377489767</v>
+        <f>freight!V37</f>
+        <v>1.6557859790084686</v>
       </c>
       <c r="T6">
-        <f>freight!W37*1.05</f>
-        <v>1.7605458865731805</v>
+        <f>freight!W37</f>
+        <v>1.6767103681649338</v>
       </c>
       <c r="U6">
-        <f>freight!X37*1.04</f>
-        <v>1.7658151488944966</v>
+        <f>freight!X37</f>
+        <v>1.6978991816293236</v>
       </c>
       <c r="V6">
-        <f>freight!Y37*1.03</f>
-        <v>1.77093643379604</v>
+        <f>freight!Y37</f>
+        <v>1.7193557609670291</v>
       </c>
       <c r="W6">
-        <f>freight!Z37*1.02</f>
-        <v>1.7759051597706748</v>
+        <f>freight!Z37</f>
+        <v>1.7410834899712497</v>
       </c>
       <c r="X6">
-        <f>freight!AA37*1.015</f>
-        <v>1.7768719420683758</v>
+        <f>freight!AA37</f>
+        <v>1.7506127508062819</v>
       </c>
       <c r="Y6">
-        <f>freight!AB37*1.01</f>
-        <v>1.7777961086573193</v>
+        <f>freight!AB37</f>
+        <v>1.7601941669874448</v>
       </c>
       <c r="Z6">
-        <f>freight!AC37*1.005</f>
-        <v>1.7786771640901122</v>
+        <f>freight!AC37</f>
+        <v>1.7698280239702611</v>
       </c>
       <c r="AA6">
         <f>freight!AD37</f>
@@ -21580,6 +21580,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -21813,15 +21822,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDFF6AF-0E01-497B-A1FE-BB038233C025}">
   <ds:schemaRefs>
@@ -21831,6 +21831,24 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0447F67E-7323-42C4-9E2C-56E0CFB6E612}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21848,22 +21866,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488A8530-D958-492E-B15F-BAB6AA6D6879}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>